--- a/AWS_Decision_Makers_Contacts.xlsx
+++ b/AWS_Decision_Makers_Contacts.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Existing AWS Accounts (126)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="AWS Lookalike Prospects (100)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Read Me" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sales Nav Searches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Existing AWS Accounts (126)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AWS Lookalike Prospects (100)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Existing AWS Accounts (126)'!$A$1:$N$168</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AWS Lookalike Prospects (100)'!$A$1:$N$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Existing AWS Accounts (126)'!$A$1:$N$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AWS Lookalike Prospects (100)'!$A$1:$N$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -100,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -150,6 +151,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,6 +520,6390 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F227"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Search: Tech decision makers (CTO/CIO/VP Eng/Head IT/Cloud/DevOps)</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>Search: Business decision makers (CEO/Founder/CFO)</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>Done?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ZOMATO MEDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22ZOMATO%20MEDIA%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22ZOMATO%20MEDIA%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Swiggy</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Swiggy%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Swiggy%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Grofers</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Grofers%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Grofers%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IndiaMart InterMesh Ltd</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22IndiaMart%20InterMesh%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22IndiaMart%20InterMesh%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DELHIVERY PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22DELHIVERY%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22DELHIVERY%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Zepto Private Limited</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zepto%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zepto%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MakeMyTrip India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22MakeMyTrip%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22MakeMyTrip%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MARUTI SUZUKI (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22MARUTI%20SUZUKI%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22MARUTI%20SUZUKI%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nykaa E-Retail Limited</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nykaa%20E-Retail%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nykaa%20E-Retail%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Travel Boutique Online (TBO)</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Travel%20Boutique%20Online%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Travel%20Boutique%20Online%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22FirstCry%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22FirstCry%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Axtria Inc</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Axtria%20Inc%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Axtria%20Inc%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jubilant Foodworks LTD</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jubilant%20Foodworks%20LTD%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jubilant%20Foodworks%20LTD%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pilani Soft Labs Pvt. Ltd. (Redbus.in)</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pilani%20Soft%20Labs%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pilani%20Soft%20Labs%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Shiprocket (BigFoot Retail Solutions Pvt.)</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shiprocket%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shiprocket%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>UrbanClap Technologies India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22UrbanClap%20Technologies%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22UrbanClap%20Technologies%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lenskart</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lenskart%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lenskart%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cars24.com</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cars24.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cars24.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CarTrade Tech Group CarWale CarTrade SAMIL OLX India</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CarTrade%20Tech%20Group%20CarWale%20CarTrade%20SAMIL%20OLX%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CarTrade%20Tech%20Group%20CarWale%20CarTrade%20SAMIL%20OLX%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Motherson Technology Services Limited</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Motherson%20Technology%20Services%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Motherson%20Technology%20Services%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hero%20MotoCorp%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hero%20MotoCorp%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Dr Reddy's Laboratories Ltd</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dr%20Reddy%27s%20Laboratories%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dr%20Reddy%27s%20Laboratories%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apollo Tyres</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Apollo%20Tyres%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Apollo%20Tyres%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>iXiGO.com</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22iXiGO.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22iXiGO.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brandix Apparels Lanka Ltd</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Brandix%20Apparels%20Lanka%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Brandix%20Apparels%20Lanka%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sampurna E-Solutions Private Ltd - PharmEasy</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sampurna%20E-Solutions%20Private%20Ltd%20-%20PharmEasy%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sampurna%20E-Solutions%20Private%20Ltd%20-%20PharmEasy%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Snapdeal</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Snapdeal%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Snapdeal%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LRN Corporation</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22LRN%20Corporation%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22LRN%20Corporation%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Allcargo Logistics Ltd.</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Allcargo%20Logistics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Allcargo%20Logistics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Travelopia Holdings Limited</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Travelopia%20Holdings%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Travelopia%20Holdings%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jubilant Life Sciences Limited</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jubilant%20Life%20Sciences%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jubilant%20Life%20Sciences%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tek Travels DMCC</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Tek%20Travels%20DMCC%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Tek%20Travels%20DMCC%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Strides Pharma Science Limited</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Strides%20Pharma%20Science%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Strides%20Pharma%20Science%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Practo Technologies Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Practo%20Technologies%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Practo%20Technologies%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DocsApp / Medibuddy</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22DocsApp%20/%20Medibuddy%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22DocsApp%20/%20Medibuddy%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DTDC Courier &amp; Cargo Limited</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22DTDC%20Courier%20%26%20Cargo%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22DTDC%20Courier%20%26%20Cargo%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CP PLUS WORLD</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CP%20PLUS%20WORLD%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CP%20PLUS%20WORLD%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TVS Motor Company Limited</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TVS%20Motor%20Company%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TVS%20Motor%20Company%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Export Trading Group</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Export%20Trading%20Group%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Export%20Trading%20Group%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Atain (Formerly IGT Solutions)</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Atain%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Atain%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Vestige Marketing</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vestige%20Marketing%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vestige%20Marketing%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Akasa Air</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akasa%20Air%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akasa%20Air%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Metro Brands Ltd</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Metro%20Brands%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Metro%20Brands%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Synergy Marine Group</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Synergy%20Marine%20Group%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Synergy%20Marine%20Group%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TripJack Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TripJack%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TripJack%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chalo.com (zophop)</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Chalo.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Chalo.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HeroFincorp</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22HeroFincorp%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22HeroFincorp%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Kirloskar Management Services Private Limited</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Kirloskar%20Management%20Services%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Kirloskar%20Management%20Services%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pet Pooja</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pet%20Pooja%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pet%20Pooja%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Bitla Software Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bitla%20Software%20Pvt.%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bitla%20Software%20Pvt.%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NEUBERG DIAGNOSTICS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22NEUBERG%20DIAGNOSTICS%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22NEUBERG%20DIAGNOSTICS%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Compass Group India</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Compass%20Group%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Compass%20Group%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SUN PHARMACEUTICAL INDUSTRIES LIMITED</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SUN%20PHARMACEUTICAL%20INDUSTRIES%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SUN%20PHARMACEUTICAL%20INDUSTRIES%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Unicommerce eSolutions</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Unicommerce%20eSolutions%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Unicommerce%20eSolutions%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Confirm Ticket Online Solutions Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Confirm%20Ticket%20Online%20Solutions%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Confirm%20Ticket%20Online%20Solutions%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Limeroad</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Limeroad%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Limeroad%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Nevilton Softech Private Limited</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nevilton%20Softech%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nevilton%20Softech%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Godrej &amp; Boyce</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Godrej%20%26%20Boyce%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Godrej%20%26%20Boyce%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Alkem Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Alkem%20Laboratories%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Alkem%20Laboratories%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FREIGHT TIGER</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22FREIGHT%20TIGER%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22FREIGHT%20TIGER%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Cashify</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cashify%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cashify%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>TCG Digital</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TCG%20Digital%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TCG%20Digital%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Spicejet Limited</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spicejet%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spicejet%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Nimbuspost</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nimbuspost%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nimbuspost%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>More Retail</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22More%20Retail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22More%20Retail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cardekho.com(GirnarSoft Pvt. Limited )</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cardekho.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cardekho.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Abhibus Services (I) Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Abhibus%20Services%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Abhibus%20Services%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>68</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RENEW POWER PVT LTD</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22RENEW%20POWER%20PVT%20LTD%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22RENEW%20POWER%20PVT%20LTD%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>69</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CureFit Healthcare Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CureFit%20Healthcare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CureFit%20Healthcare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>70</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Malabar Group</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Malabar%20Group%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Malabar%20Group%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>71</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Rebel Foods</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rebel%20Foods%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rebel%20Foods%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>72</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Yamaha Motor India</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yamaha%20Motor%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yamaha%20Motor%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>73</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Daily Rounds</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Daily%20Rounds%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Daily%20Rounds%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>74</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>UPL LIMITED</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22UPL%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22UPL%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>75</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>nurture.farm</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22nurture.farm%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22nurture.farm%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>76</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Hero Electronix Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hero%20Electronix%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hero%20Electronix%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>77</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GRT Jewellers</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22GRT%20Jewellers%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22GRT%20Jewellers%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>78</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EIH Ltd (Oberoi Hotels)</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22EIH%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22EIH%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>79</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Green Agrevolution Private Limited</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Green%20Agrevolution%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Green%20Agrevolution%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>80</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Pickrr</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pickrr%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pickrr%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>81</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Healthians</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Healthians%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Healthians%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>82</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SENCO</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SENCO%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SENCO%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>83</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>COCOBLU RETAIL LIMITED</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22COCOBLU%20RETAIL%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22COCOBLU%20RETAIL%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>84</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ashok Leyland</t>
+        </is>
+      </c>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Ashok%20Leyland%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Ashok%20Leyland%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>85</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BlueBrix Health</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlueBrix%20Health%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlueBrix%20Health%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>86</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Oyo Rooms</t>
+        </is>
+      </c>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Oyo%20Rooms%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Oyo%20Rooms%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>87</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Cashkaro.com</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cashkaro.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cashkaro.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>88</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Kalyan Jewellers</t>
+        </is>
+      </c>
+      <c r="D89" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Kalyan%20Jewellers%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Kalyan%20Jewellers%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>89</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Innova Market Insights</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Innova%20Market%20Insights%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Innova%20Market%20Insights%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>90</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Imagine Marketing Pvt. Ltd (Boat)</t>
+        </is>
+      </c>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Imagine%20Marketing%20Pvt.%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Imagine%20Marketing%20Pvt.%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>91</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Lynk Logistics Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lynk%20Logistics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lynk%20Logistics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>92</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Yatra.com</t>
+        </is>
+      </c>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yatra.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yatra.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>93</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CLICKTECH RETAIL PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="D94" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CLICKTECH%20RETAIL%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CLICKTECH%20RETAIL%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>94</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TVS Supply Chain Solutions Limited</t>
+        </is>
+      </c>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TVS%20Supply%20Chain%20Solutions%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TVS%20Supply%20Chain%20Solutions%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>95</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Hatsun Agro Products</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hatsun%20Agro%20Products%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hatsun%20Agro%20Products%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>96</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>THERMAX LIMITED</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22THERMAX%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22THERMAX%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>97</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Eatclub Brands</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Eatclub%20Brands%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Eatclub%20Brands%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>98</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Jyothy Laboratories</t>
+        </is>
+      </c>
+      <c r="D99" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jyothy%20Laboratories%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jyothy%20Laboratories%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>99</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Wellness Forever Medicare Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wellness%20Forever%20Medicare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wellness%20Forever%20Medicare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bright Lifecare Pvt. Ltd.(HealthKart)</t>
+        </is>
+      </c>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bright%20Lifecare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bright%20Lifecare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>101</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Angara.com</t>
+        </is>
+      </c>
+      <c r="D102" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Angara.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Angara.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>102</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Aliaxis - ASHIRVAD PIPES PVT. LTD.</t>
+        </is>
+      </c>
+      <c r="D103" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aliaxis%20-%20ASHIRVAD%20PIPES%20PVT.%20LTD.%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aliaxis%20-%20ASHIRVAD%20PIPES%20PVT.%20LTD.%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>103</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Applied Research International Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Applied%20Research%20International%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Applied%20Research%20International%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>104</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Inventia Healthcare Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D105" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Inventia%20Healthcare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Inventia%20Healthcare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>105</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Hardcastle Restaurants Private Limited</t>
+        </is>
+      </c>
+      <c r="D106" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hardcastle%20Restaurants%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hardcastle%20Restaurants%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>106</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="D107" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Torrent%20Pharmaceuticals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Torrent%20Pharmaceuticals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>107</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Bajaj Electricals Ltd.</t>
+        </is>
+      </c>
+      <c r="D108" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bajaj%20Electricals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bajaj%20Electricals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>108</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Rain Industries LIMITED</t>
+        </is>
+      </c>
+      <c r="D109" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rain%20Industries%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rain%20Industries%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>109</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dishman Pharmaceuticals and Chemicals Ltd.</t>
+        </is>
+      </c>
+      <c r="D110" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dishman%20Pharmaceuticals%20and%20Chemicals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dishman%20Pharmaceuticals%20and%20Chemicals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>110</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Continue Lifesciences Private Limited</t>
+        </is>
+      </c>
+      <c r="D111" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Continue%20Lifesciences%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Continue%20Lifesciences%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>111</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Brigade Enterprises Ltd</t>
+        </is>
+      </c>
+      <c r="D112" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Brigade%20Enterprises%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Brigade%20Enterprises%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>112</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Intermiles (Jet Privilege Private Limited)</t>
+        </is>
+      </c>
+      <c r="D113" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Intermiles%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Intermiles%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>113</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Prestige Constructions</t>
+        </is>
+      </c>
+      <c r="D114" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Prestige%20Constructions%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E114" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Prestige%20Constructions%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>114</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Gmmco Limited</t>
+        </is>
+      </c>
+      <c r="D115" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Gmmco%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Gmmco%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>115</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Panasonic India</t>
+        </is>
+      </c>
+      <c r="D116" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Panasonic%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Panasonic%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>116</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ReNew Power</t>
+        </is>
+      </c>
+      <c r="D117" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22ReNew%20Power%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22ReNew%20Power%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>117</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Aira Matrix</t>
+        </is>
+      </c>
+      <c r="D118" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aira%20Matrix%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aira%20Matrix%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>118</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Torrent Power Ltd.</t>
+        </is>
+      </c>
+      <c r="D119" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Torrent%20Power%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Torrent%20Power%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>119</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ECU Worldwide</t>
+        </is>
+      </c>
+      <c r="D120" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22ECU%20Worldwide%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22ECU%20Worldwide%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>120</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Honasa Consumer Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="D121" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Honasa%20Consumer%20Pvt.%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E121" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Honasa%20Consumer%20Pvt.%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>121</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SYNGENE INTERNATIONAL LIMITED</t>
+        </is>
+      </c>
+      <c r="D122" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SYNGENE%20INTERNATIONAL%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E122" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SYNGENE%20INTERNATIONAL%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>122</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Cadila Healthcare Ltd., Ahmedabad</t>
+        </is>
+      </c>
+      <c r="D123" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cadila%20Healthcare%20%2C%20Ahmedabad%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E123" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cadila%20Healthcare%20%2C%20Ahmedabad%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>123</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ceat Tyres Limited</t>
+        </is>
+      </c>
+      <c r="D124" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Ceat%20Tyres%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E124" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Ceat%20Tyres%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>124</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Honda Motorcycle and Scooter India</t>
+        </is>
+      </c>
+      <c r="D125" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Honda%20Motorcycle%20and%20Scooter%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Honda%20Motorcycle%20and%20Scooter%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>125</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Heritage Foods Ltd.</t>
+        </is>
+      </c>
+      <c r="D126" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Heritage%20Foods%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E126" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Heritage%20Foods%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Existing AWS</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>126</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CK Birla Hospitals</t>
+        </is>
+      </c>
+      <c r="D127" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CK%20Birla%20Hospitals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E127" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CK%20Birla%20Hospitals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Licious (Delightful Gourmet)</t>
+        </is>
+      </c>
+      <c r="D128" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Licious%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E128" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Licious%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Country Delight</t>
+        </is>
+      </c>
+      <c r="D129" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Country%20Delight%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E129" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Country%20Delight%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Truemeds</t>
+        </is>
+      </c>
+      <c r="D130" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Truemeds%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E130" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Truemeds%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>4</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Treebo Hotels</t>
+        </is>
+      </c>
+      <c r="D131" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Treebo%20Hotels%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Treebo%20Hotels%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>5</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Yulu Bikes</t>
+        </is>
+      </c>
+      <c r="D132" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yulu%20Bikes%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yulu%20Bikes%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>6</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DealShare</t>
+        </is>
+      </c>
+      <c r="D133" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22DealShare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E133" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22DealShare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>7</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Spencer's Retail</t>
+        </is>
+      </c>
+      <c r="D134" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spencer%27s%20Retail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spencer%27s%20Retail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>8</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Medanta (Global Health)</t>
+        </is>
+      </c>
+      <c r="D135" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Medanta%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Medanta%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>9</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>carandbike (Mahindra)</t>
+        </is>
+      </c>
+      <c r="D136" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22carandbike%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22carandbike%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>10</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>The Souled Store</t>
+        </is>
+      </c>
+      <c r="D137" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Souled%20Store%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E137" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Souled%20Store%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>11</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Quick Ride</t>
+        </is>
+      </c>
+      <c r="D138" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Quick%20Ride%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Quick%20Ride%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>12</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>OfBusiness</t>
+        </is>
+      </c>
+      <c r="D139" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22OfBusiness%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E139" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22OfBusiness%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>13</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Dr Lal PathLabs</t>
+        </is>
+      </c>
+      <c r="D140" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dr%20Lal%20PathLabs%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dr%20Lal%20PathLabs%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>14</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Orange Health Labs</t>
+        </is>
+      </c>
+      <c r="D141" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Orange%20Health%20Labs%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E141" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Orange%20Health%20Labs%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>15</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Medikabazaar</t>
+        </is>
+      </c>
+      <c r="D142" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Medikabazaar%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Medikabazaar%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>16</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Woodland (Aero Club)</t>
+        </is>
+      </c>
+      <c r="D143" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Woodland%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E143" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Woodland%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>17</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FarMart</t>
+        </is>
+      </c>
+      <c r="D144" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22FarMart%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22FarMart%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>18</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Nature's Basket</t>
+        </is>
+      </c>
+      <c r="D145" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nature%27s%20Basket%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E145" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nature%27s%20Basket%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>19</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Hopscotch</t>
+        </is>
+      </c>
+      <c r="D146" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hopscotch%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hopscotch%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>20</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Orient Electric</t>
+        </is>
+      </c>
+      <c r="D147" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Orient%20Electric%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Orient%20Electric%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>21</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>BOX8 (Eatsure)</t>
+        </is>
+      </c>
+      <c r="D148" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22BOX8%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22BOX8%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>22</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
+        </is>
+      </c>
+      <c r="D149" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shipsy%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E149" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shipsy%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>23</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Locus</t>
+        </is>
+      </c>
+      <c r="D150" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Locus%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Locus%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>24</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Moglix</t>
+        </is>
+      </c>
+      <c r="D151" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Moglix%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E151" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Moglix%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>25</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Metropolis Healthcare</t>
+        </is>
+      </c>
+      <c r="D152" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Metropolis%20Healthcare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E152" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Metropolis%20Healthcare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>26</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AgroStar</t>
+        </is>
+      </c>
+      <c r="D153" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22AgroStar%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E153" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22AgroStar%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>27</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="D154" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akshayakalpa%20Organic%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akshayakalpa%20Organic%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>28</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CaratLane</t>
+        </is>
+      </c>
+      <c r="D155" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CaratLane%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E155" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CaratLane%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>29</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Foxtale</t>
+        </is>
+      </c>
+      <c r="D156" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Foxtale%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Foxtale%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>30</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CityMall</t>
+        </is>
+      </c>
+      <c r="D157" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CityMall%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E157" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CityMall%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>31</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Vegrow</t>
+        </is>
+      </c>
+      <c r="D158" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vegrow%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E158" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vegrow%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>32</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Shree Maruti Courier</t>
+        </is>
+      </c>
+      <c r="D159" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shree%20Maruti%20Courier%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E159" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shree%20Maruti%20Courier%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>33</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Pickyourtrail</t>
+        </is>
+      </c>
+      <c r="D160" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pickyourtrail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E160" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pickyourtrail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>34</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Urban Ladder</t>
+        </is>
+      </c>
+      <c r="D161" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Urban%20Ladder%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E161" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Urban%20Ladder%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>35</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>BlueStone</t>
+        </is>
+      </c>
+      <c r="D162" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlueStone%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E162" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlueStone%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>36</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Zivame</t>
+        </is>
+      </c>
+      <c r="D163" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zivame%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E163" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zivame%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>37</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Clovia</t>
+        </is>
+      </c>
+      <c r="D164" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Clovia%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E164" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Clovia%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>38</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Noise</t>
+        </is>
+      </c>
+      <c r="D165" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Noise%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E165" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Noise%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>39</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="D166" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Chai%20Point%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E166" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Chai%20Point%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>40</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>BlackBuck (Zinka Logistics)</t>
+        </is>
+      </c>
+      <c r="D167" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlackBuck%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E167" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlackBuck%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>41</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Veena World</t>
+        </is>
+      </c>
+      <c r="D168" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Veena%20World%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E168" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Veena%20World%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>42</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Zostel</t>
+        </is>
+      </c>
+      <c r="D169" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zostel%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E169" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zostel%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>43</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Revv</t>
+        </is>
+      </c>
+      <c r="D170" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Revv%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E170" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Revv%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>44</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Cogoport</t>
+        </is>
+      </c>
+      <c r="D171" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cogoport%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E171" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cogoport%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>45</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Zetwerk</t>
+        </is>
+      </c>
+      <c r="D172" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zetwerk%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E172" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zetwerk%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>46</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Bizongo</t>
+        </is>
+      </c>
+      <c r="D173" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bizongo%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E173" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bizongo%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>47</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Pristyn Care</t>
+        </is>
+      </c>
+      <c r="D174" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pristyn%20Care%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E174" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pristyn%20Care%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>48</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Vijay Sales</t>
+        </is>
+      </c>
+      <c r="D175" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vijay%20Sales%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E175" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vijay%20Sales%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>49</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Voylla</t>
+        </is>
+      </c>
+      <c r="D176" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Voylla%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E176" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Voylla%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>50</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Blue Tokai Coffee</t>
+        </is>
+      </c>
+      <c r="D177" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Blue%20Tokai%20Coffee%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Blue%20Tokai%20Coffee%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>51</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>HealthifyMe</t>
+        </is>
+      </c>
+      <c r="D178" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22HealthifyMe%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E178" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22HealthifyMe%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>52</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Fitterfly</t>
+        </is>
+      </c>
+      <c r="D179" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Fitterfly%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E179" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Fitterfly%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>53</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>MFine</t>
+        </is>
+      </c>
+      <c r="D180" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22MFine%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E180" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22MFine%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>54</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Zeno Health</t>
+        </is>
+      </c>
+      <c r="D181" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zeno%20Health%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E181" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zeno%20Health%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>55</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Khadim's</t>
+        </is>
+      </c>
+      <c r="D182" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Khadim%27s%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E182" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Khadim%27s%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>56</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Aditya Birla Fashion (Pantaloons, Allen Solly, Peter England, Van Heusen, Louis Philippe – all on Route 53/ap-south-1)</t>
+        </is>
+      </c>
+      <c r="D183" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aditya%20Birla%20Fashion%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E183" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aditya%20Birla%20Fashion%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>57</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>La Pino'z Pizza</t>
+        </is>
+      </c>
+      <c r="D184" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22La%20Pino%27z%20Pizza%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E184" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22La%20Pino%27z%20Pizza%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>58</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Lybrate</t>
+        </is>
+      </c>
+      <c r="D185" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lybrate%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E185" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lybrate%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>59</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Rainbow Children's Hospital</t>
+        </is>
+      </c>
+      <c r="D186" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rainbow%20Children%27s%20Hospital%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E186" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rainbow%20Children%27s%20Hospital%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>60</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare</t>
+        </is>
+      </c>
+      <c r="D187" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aster%20DM%20Healthcare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E187" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aster%20DM%20Healthcare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>61</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>VLCC Personal Care</t>
+        </is>
+      </c>
+      <c r="D188" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22VLCC%20Personal%20Care%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E188" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22VLCC%20Personal%20Care%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>62</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Titan Eye+</t>
+        </is>
+      </c>
+      <c r="D189" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Titan%20Eye%2B%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E189" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Titan%20Eye%2B%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>63</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Godrej Interio</t>
+        </is>
+      </c>
+      <c r="D190" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Godrej%20Interio%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E190" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Godrej%20Interio%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>64</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Berger Paints</t>
+        </is>
+      </c>
+      <c r="D191" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Berger%20Paints%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E191" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Berger%20Paints%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>65</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Greenply Industries</t>
+        </is>
+      </c>
+      <c r="D192" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Greenply%20Industries%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E192" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Greenply%20Industries%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>66</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Trackon Couriers</t>
+        </is>
+      </c>
+      <c r="D193" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Trackon%20Couriers%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E193" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Trackon%20Couriers%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>67</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Pepperfry</t>
+        </is>
+      </c>
+      <c r="D194" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pepperfry%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E194" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pepperfry%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>68</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Wakefit</t>
+        </is>
+      </c>
+      <c r="D195" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wakefit%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E195" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wakefit%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>69</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Wow! Momo</t>
+        </is>
+      </c>
+      <c r="D196" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wow%21%20Momo%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E196" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wow%21%20Momo%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>70</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>XpressBees</t>
+        </is>
+      </c>
+      <c r="D197" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22XpressBees%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E197" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22XpressBees%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>71</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Shadowfax</t>
+        </is>
+      </c>
+      <c r="D198" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shadowfax%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E198" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shadowfax%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>72</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>iThink Logistics</t>
+        </is>
+      </c>
+      <c r="D199" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22iThink%20Logistics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E199" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22iThink%20Logistics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>73</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Akbar Travels</t>
+        </is>
+      </c>
+      <c r="D200" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akbar%20Travels%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E200" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akbar%20Travels%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>74</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>FarEye</t>
+        </is>
+      </c>
+      <c r="D201" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22FarEye%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E201" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22FarEye%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>75</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Jumbotail</t>
+        </is>
+      </c>
+      <c r="D202" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jumbotail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E202" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jumbotail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>76</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Thyrocare</t>
+        </is>
+      </c>
+      <c r="D203" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Thyrocare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E203" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Thyrocare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>77</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Manipal Hospitals</t>
+        </is>
+      </c>
+      <c r="D204" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Manipal%20Hospitals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E204" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Manipal%20Hospitals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>78</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>CarInfo</t>
+        </is>
+      </c>
+      <c r="D205" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CarInfo%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E205" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22CarInfo%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>79</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Park+</t>
+        </is>
+      </c>
+      <c r="D206" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Park%2B%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E206" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Park%2B%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>80</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Sangeetha Mobiles</t>
+        </is>
+      </c>
+      <c r="D207" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sangeetha%20Mobiles%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E207" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sangeetha%20Mobiles%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>81</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>The Whole Truth Foods</t>
+        </is>
+      </c>
+      <c r="D208" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Whole%20Truth%20Foods%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E208" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Whole%20Truth%20Foods%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>82</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Raw Pressery</t>
+        </is>
+      </c>
+      <c r="D209" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Raw%20Pressery%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E209" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Raw%20Pressery%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>83</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Nestasia</t>
+        </is>
+      </c>
+      <c r="D210" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nestasia%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E210" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nestasia%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>84</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>KisanKonnect</t>
+        </is>
+      </c>
+      <c r="D211" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22KisanKonnect%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E211" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22KisanKonnect%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>85</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Raymond</t>
+        </is>
+      </c>
+      <c r="D212" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Raymond%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E212" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Raymond%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>86</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>V-Guard Industries</t>
+        </is>
+      </c>
+      <c r="D213" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22V-Guard%20Industries%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E213" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22V-Guard%20Industries%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>87</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Spoton Logistics</t>
+        </is>
+      </c>
+      <c r="D214" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spoton%20Logistics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E214" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spoton%20Logistics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>88</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>TripFactory</t>
+        </is>
+      </c>
+      <c r="D215" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TripFactory%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E215" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22TripFactory%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>89</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Plum Goodness</t>
+        </is>
+      </c>
+      <c r="D216" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Plum%20Goodness%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E216" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Plum%20Goodness%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>90</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Zoomcar</t>
+        </is>
+      </c>
+      <c r="D217" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zoomcar%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E217" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zoomcar%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>91</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>V-Mart Retail</t>
+        </is>
+      </c>
+      <c r="D218" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22V-Mart%20Retail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E218" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22V-Mart%20Retail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>92</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SuperK</t>
+        </is>
+      </c>
+      <c r="D219" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SuperK%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E219" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SuperK%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>93</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Naturals Salon</t>
+        </is>
+      </c>
+      <c r="D220" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Naturals%20Salon%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E220" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Naturals%20Salon%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>94</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>The Body Shop India</t>
+        </is>
+      </c>
+      <c r="D221" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Body%20Shop%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E221" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Body%20Shop%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>95</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Forest Essentials</t>
+        </is>
+      </c>
+      <c r="D222" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Forest%20Essentials%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E222" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Forest%20Essentials%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>96</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Safexpress</t>
+        </is>
+      </c>
+      <c r="D223" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Safexpress%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E223" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Safexpress%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>97</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Sarovar Hotels</t>
+        </is>
+      </c>
+      <c r="D224" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sarovar%20Hotels%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E224" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sarovar%20Hotels%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>98</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SUGAR Cosmetics</t>
+        </is>
+      </c>
+      <c r="D225" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SUGAR%20Cosmetics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E225" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22SUGAR%20Cosmetics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>99</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Emami</t>
+        </is>
+      </c>
+      <c r="D226" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Emami%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E226" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Emami%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>100</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Melorra</t>
+        </is>
+      </c>
+      <c r="D227" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Melorra%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+        </is>
+      </c>
+      <c r="E227" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=%22Melorra%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10621,7 +17010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18611,7 +25000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/AWS_Decision_Makers_Contacts.xlsx
+++ b/AWS_Decision_Makers_Contacts.xlsx
@@ -520,15 +520,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,15 +551,25 @@
       </c>
       <c r="D1" s="17" t="inlineStr">
         <is>
-          <t>Search: Tech decision makers (CTO/CIO/VP Eng/Head IT/Cloud/DevOps)</t>
+          <t>Search name used</t>
         </is>
       </c>
       <c r="E1" s="17" t="inlineStr">
         <is>
-          <t>Search: Business decision makers (CEO/Founder/CFO)</t>
+          <t>Filtered search: Company + Seniority (CXO/VP/Director/Owner) + Function (IT/Engineering)</t>
         </is>
       </c>
       <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>Filtered search: Company + Seniority only (all functions)</t>
+        </is>
+      </c>
+      <c r="G1" s="17" t="inlineStr">
+        <is>
+          <t>Simple keyword search (company name)</t>
+        </is>
+      </c>
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>Done?</t>
         </is>
@@ -577,17 +589,27 @@
           <t>ZOMATO MEDIA PRIVATE LIMITED</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22ZOMATO%20MEDIA%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ZOMATO MEDIA</t>
         </is>
       </c>
       <c r="E2" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22ZOMATO%20MEDIA%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZOMATO%20MEDIA%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZOMATO%20MEDIA%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=ZOMATO%20MEDIA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -603,17 +625,27 @@
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Swiggy%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Swiggy</t>
         </is>
       </c>
       <c r="E3" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Swiggy%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASwiggy%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASwiggy%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Swiggy</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,17 +661,27 @@
           <t>Grofers</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Grofers%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Grofers</t>
         </is>
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Grofers%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGrofers%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGrofers%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Grofers</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -655,17 +697,27 @@
           <t>IndiaMart InterMesh Ltd</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22IndiaMart%20InterMesh%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IndiaMart InterMesh Ltd</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22IndiaMart%20InterMesh%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AIndiaMart%20InterMesh%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AIndiaMart%20InterMesh%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=IndiaMart%20InterMesh%20Ltd</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -681,17 +733,27 @@
           <t>DELHIVERY PRIVATE LIMITED</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22DELHIVERY%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22DELHIVERY%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADELHIVERY%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADELHIVERY%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=DELHIVERY</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -707,17 +769,27 @@
           <t>Zepto Private Limited</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zepto%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Zepto</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zepto%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZepto%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZepto%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Zepto</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -733,17 +805,27 @@
           <t>MakeMyTrip India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22MakeMyTrip%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MakeMyTrip India</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22MakeMyTrip%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMakeMyTrip%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMakeMyTrip%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=MakeMyTrip%20India</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -759,17 +841,27 @@
           <t>MARUTI SUZUKI (INDIA) LIMITED</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22MARUTI%20SUZUKI%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MARUTI SUZUKI</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22MARUTI%20SUZUKI%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMARUTI%20SUZUKI%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMARUTI%20SUZUKI%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=MARUTI%20SUZUKI</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -785,17 +877,27 @@
           <t>Nykaa E-Retail Limited</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nykaa%20E-Retail%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Nykaa E-Retail Limited</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nykaa%20E-Retail%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANykaa%20E-Retail%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANykaa%20E-Retail%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Nykaa%20E-Retail%20Limited</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,17 +913,27 @@
           <t>Travel Boutique Online (TBO)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Travel%20Boutique%20Online%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Travel Boutique Online</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Travel%20Boutique%20Online%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATravel%20Boutique%20Online%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATravel%20Boutique%20Online%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Travel%20Boutique%20Online</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -837,17 +949,27 @@
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22FirstCry%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22FirstCry%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFirstCry%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFirstCry%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=FirstCry</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -863,17 +985,27 @@
           <t>Axtria Inc</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Axtria%20Inc%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Axtria Inc</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Axtria%20Inc%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAxtria%20Inc%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAxtria%20Inc%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Axtria%20Inc</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -889,17 +1021,27 @@
           <t>Jubilant Foodworks LTD</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jubilant%20Foodworks%20LTD%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jubilant Foodworks LTD</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jubilant%20Foodworks%20LTD%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AJubilant%20Foodworks%20LTD%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AJubilant%20Foodworks%20LTD%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Jubilant%20Foodworks%20LTD</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -915,17 +1057,27 @@
           <t>Pilani Soft Labs Pvt. Ltd. (Redbus.in)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pilani%20Soft%20Labs%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pilani Soft Labs</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pilani%20Soft%20Labs%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APilani%20Soft%20Labs%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APilani%20Soft%20Labs%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Pilani%20Soft%20Labs</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -941,17 +1093,27 @@
           <t>Shiprocket (BigFoot Retail Solutions Pvt.)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shiprocket%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Shiprocket</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shiprocket%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AShiprocket%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AShiprocket%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Shiprocket</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,17 +1129,27 @@
           <t>UrbanClap Technologies India Pvt Ltd</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22UrbanClap%20Technologies%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>UrbanClap Technologies India</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22UrbanClap%20Technologies%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AUrbanClap%20Technologies%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AUrbanClap%20Technologies%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=UrbanClap%20Technologies%20India</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -993,17 +1165,27 @@
           <t>Lenskart</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lenskart%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lenskart</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lenskart%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALenskart%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALenskart%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Lenskart</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1019,17 +1201,27 @@
           <t>Cars24.com</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cars24.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cars24.com</t>
         </is>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cars24.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACars24.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACars24.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Cars24.com</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1045,17 +1237,27 @@
           <t>CarTrade Tech Group CarWale CarTrade SAMIL OLX India</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CarTrade%20Tech%20Group%20CarWale%20CarTrade%20SAMIL%20OLX%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CarTrade Tech Group CarWale CarTrade SAMIL OLX India</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CarTrade%20Tech%20Group%20CarWale%20CarTrade%20SAMIL%20OLX%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACarTrade%20Tech%20Group%20CarWale%20CarTrade%20SAMIL%20OLX%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACarTrade%20Tech%20Group%20CarWale%20CarTrade%20SAMIL%20OLX%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=CarTrade%20Tech%20Group%20CarWale%20CarTrade%20SAMIL%20OLX%20India</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1071,17 +1273,27 @@
           <t>Motherson Technology Services Limited</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Motherson%20Technology%20Services%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Motherson Technology Services Limited</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Motherson%20Technology%20Services%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMotherson%20Technology%20Services%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMotherson%20Technology%20Services%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Motherson%20Technology%20Services%20Limited</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1097,17 +1309,27 @@
           <t>Hero MotoCorp</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hero%20MotoCorp%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp</t>
         </is>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hero%20MotoCorp%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHero%20MotoCorp%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHero%20MotoCorp%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Hero%20MotoCorp</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1123,17 +1345,27 @@
           <t>Dr Reddy's Laboratories Ltd</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dr%20Reddy%27s%20Laboratories%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Dr Reddy's Laboratories Ltd</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dr%20Reddy%27s%20Laboratories%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADr%20Reddy%27s%20Laboratories%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADr%20Reddy%27s%20Laboratories%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Dr%20Reddy%27s%20Laboratories%20Ltd</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1149,17 +1381,27 @@
           <t>Apollo Tyres</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Apollo%20Tyres%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Apollo Tyres</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Apollo%20Tyres%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AApollo%20Tyres%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AApollo%20Tyres%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Apollo%20Tyres</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1175,17 +1417,27 @@
           <t>iXiGO.com</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22iXiGO.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>iXiGO.com</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22iXiGO.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AiXiGO.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AiXiGO.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=iXiGO.com</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1201,17 +1453,27 @@
           <t>Brandix Apparels Lanka Ltd</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Brandix%20Apparels%20Lanka%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Brandix Apparels Lanka Ltd</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Brandix%20Apparels%20Lanka%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABrandix%20Apparels%20Lanka%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABrandix%20Apparels%20Lanka%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Brandix%20Apparels%20Lanka%20Ltd</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1227,17 +1489,27 @@
           <t>Sampurna E-Solutions Private Ltd - PharmEasy</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sampurna%20E-Solutions%20Private%20Ltd%20-%20PharmEasy%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sampurna E-Solutions Private Ltd - PharmEasy</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sampurna%20E-Solutions%20Private%20Ltd%20-%20PharmEasy%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASampurna%20E-Solutions%20Private%20Ltd%20-%20PharmEasy%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASampurna%20E-Solutions%20Private%20Ltd%20-%20PharmEasy%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Sampurna%20E-Solutions%20Private%20Ltd%20-%20PharmEasy</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1253,17 +1525,27 @@
           <t>Snapdeal</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Snapdeal%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Snapdeal</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Snapdeal%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASnapdeal%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASnapdeal%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Snapdeal</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1279,17 +1561,27 @@
           <t>LRN Corporation</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22LRN%20Corporation%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LRN Corporation</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22LRN%20Corporation%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALRN%20Corporation%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALRN%20Corporation%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=LRN%20Corporation</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1305,17 +1597,27 @@
           <t>Allcargo Logistics Ltd.</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Allcargo%20Logistics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Allcargo Logistics</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Allcargo%20Logistics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAllcargo%20Logistics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAllcargo%20Logistics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Allcargo%20Logistics</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1331,17 +1633,27 @@
           <t>Travelopia Holdings Limited</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Travelopia%20Holdings%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Travelopia Holdings Limited</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Travelopia%20Holdings%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATravelopia%20Holdings%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATravelopia%20Holdings%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Travelopia%20Holdings%20Limited</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1357,17 +1669,27 @@
           <t>Jubilant Life Sciences Limited</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jubilant%20Life%20Sciences%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jubilant Life Sciences Limited</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jubilant%20Life%20Sciences%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AJubilant%20Life%20Sciences%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AJubilant%20Life%20Sciences%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Jubilant%20Life%20Sciences%20Limited</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1383,17 +1705,27 @@
           <t>Tek Travels DMCC</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Tek%20Travels%20DMCC%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tek Travels DMCC</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Tek%20Travels%20DMCC%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATek%20Travels%20DMCC%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATek%20Travels%20DMCC%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Tek%20Travels%20DMCC</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1409,17 +1741,27 @@
           <t>Strides Pharma Science Limited</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Strides%20Pharma%20Science%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Strides Pharma Science Limited</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Strides%20Pharma%20Science%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AStrides%20Pharma%20Science%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AStrides%20Pharma%20Science%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Strides%20Pharma%20Science%20Limited</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1435,17 +1777,27 @@
           <t>Practo Technologies Pvt Ltd</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Practo%20Technologies%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Practo Technologies</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Practo%20Technologies%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APracto%20Technologies%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APracto%20Technologies%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Practo%20Technologies</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1461,17 +1813,27 @@
           <t>DocsApp / Medibuddy</t>
         </is>
       </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22DocsApp%20/%20Medibuddy%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DocsApp Medibuddy</t>
         </is>
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22DocsApp%20/%20Medibuddy%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADocsApp%20Medibuddy%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADocsApp%20Medibuddy%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=DocsApp%20Medibuddy</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1487,17 +1849,27 @@
           <t>DTDC Courier &amp; Cargo Limited</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22DTDC%20Courier%20%26%20Cargo%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DTDC Courier &amp; Cargo Limited</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22DTDC%20Courier%20%26%20Cargo%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADTDC%20Courier%20%26%20Cargo%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADTDC%20Courier%20%26%20Cargo%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=DTDC%20Courier%20%26%20Cargo%20Limited</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1513,17 +1885,27 @@
           <t>CP PLUS WORLD</t>
         </is>
       </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CP%20PLUS%20WORLD%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CP PLUS WORLD</t>
         </is>
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CP%20PLUS%20WORLD%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACP%20PLUS%20WORLD%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACP%20PLUS%20WORLD%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=CP%20PLUS%20WORLD</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1539,17 +1921,27 @@
           <t>TVS Motor Company Limited</t>
         </is>
       </c>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TVS%20Motor%20Company%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TVS Motor Company Limited</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TVS%20Motor%20Company%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATVS%20Motor%20Company%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATVS%20Motor%20Company%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=TVS%20Motor%20Company%20Limited</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1565,17 +1957,27 @@
           <t>Export Trading Group</t>
         </is>
       </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Export%20Trading%20Group%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Export Trading Group</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Export%20Trading%20Group%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AExport%20Trading%20Group%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AExport%20Trading%20Group%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Export%20Trading%20Group</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1591,17 +1993,27 @@
           <t>Atain (Formerly IGT Solutions)</t>
         </is>
       </c>
-      <c r="D41" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Atain%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Atain</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Atain%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAtain%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAtain%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Atain</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1617,17 +2029,27 @@
           <t>Vestige Marketing</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vestige%20Marketing%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Vestige Marketing</t>
         </is>
       </c>
       <c r="E42" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vestige%20Marketing%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVestige%20Marketing%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVestige%20Marketing%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Vestige%20Marketing</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1643,17 +2065,27 @@
           <t>Akasa Air</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akasa%20Air%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akasa%20Air%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAkasa%20Air%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAkasa%20Air%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Akasa%20Air</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1669,17 +2101,27 @@
           <t>Metro Brands Ltd</t>
         </is>
       </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Metro%20Brands%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Metro Brands Ltd</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Metro%20Brands%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMetro%20Brands%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMetro%20Brands%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Metro%20Brands%20Ltd</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1695,17 +2137,27 @@
           <t>Synergy Marine Group</t>
         </is>
       </c>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Synergy%20Marine%20Group%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Synergy Marine Group</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Synergy%20Marine%20Group%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASynergy%20Marine%20Group%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASynergy%20Marine%20Group%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Synergy%20Marine%20Group</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1721,17 +2173,27 @@
           <t>TripJack Pvt Ltd</t>
         </is>
       </c>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TripJack%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TripJack</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TripJack%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATripJack%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATripJack%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=TripJack</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1747,17 +2209,27 @@
           <t>Chalo.com (zophop)</t>
         </is>
       </c>
-      <c r="D47" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Chalo.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Chalo.com</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Chalo.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AChalo.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AChalo.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Chalo.com</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1773,17 +2245,27 @@
           <t>HeroFincorp</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22HeroFincorp%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HeroFincorp</t>
         </is>
       </c>
       <c r="E48" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22HeroFincorp%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHeroFincorp%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHeroFincorp%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=HeroFincorp</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1799,17 +2281,27 @@
           <t>Kirloskar Management Services Private Limited</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Kirloskar%20Management%20Services%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Kirloskar Management Services</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Kirloskar%20Management%20Services%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AKirloskar%20Management%20Services%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AKirloskar%20Management%20Services%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Kirloskar%20Management%20Services</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1825,17 +2317,27 @@
           <t>Pet Pooja</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pet%20Pooja%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pet Pooja</t>
         </is>
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pet%20Pooja%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APet%20Pooja%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APet%20Pooja%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Pet%20Pooja</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1851,17 +2353,27 @@
           <t>Bitla Software Pvt. Ltd</t>
         </is>
       </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bitla%20Software%20Pvt.%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bitla Software Pvt. Ltd</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bitla%20Software%20Pvt.%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABitla%20Software%20Pvt.%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABitla%20Software%20Pvt.%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Bitla%20Software%20Pvt.%20Ltd</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1877,17 +2389,27 @@
           <t>NEUBERG DIAGNOSTICS PRIVATE LIMITED</t>
         </is>
       </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22NEUBERG%20DIAGNOSTICS%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NEUBERG DIAGNOSTICS</t>
         </is>
       </c>
       <c r="E52" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22NEUBERG%20DIAGNOSTICS%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANEUBERG%20DIAGNOSTICS%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANEUBERG%20DIAGNOSTICS%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=NEUBERG%20DIAGNOSTICS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1903,17 +2425,27 @@
           <t>Compass Group India</t>
         </is>
       </c>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Compass%20Group%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Compass Group India</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Compass%20Group%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACompass%20Group%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACompass%20Group%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G53" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Compass%20Group%20India</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1929,17 +2461,27 @@
           <t>SUN PHARMACEUTICAL INDUSTRIES LIMITED</t>
         </is>
       </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SUN%20PHARMACEUTICAL%20INDUSTRIES%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SUN PHARMACEUTICAL INDUSTRIES</t>
         </is>
       </c>
       <c r="E54" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SUN%20PHARMACEUTICAL%20INDUSTRIES%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASUN%20PHARMACEUTICAL%20INDUSTRIES%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASUN%20PHARMACEUTICAL%20INDUSTRIES%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=SUN%20PHARMACEUTICAL%20INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1955,17 +2497,27 @@
           <t>Unicommerce eSolutions</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Unicommerce%20eSolutions%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Unicommerce eSolutions</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Unicommerce%20eSolutions%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AUnicommerce%20eSolutions%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AUnicommerce%20eSolutions%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Unicommerce%20eSolutions</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1981,17 +2533,27 @@
           <t>Confirm Ticket Online Solutions Pvt Ltd</t>
         </is>
       </c>
-      <c r="D56" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Confirm%20Ticket%20Online%20Solutions%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Confirm Ticket Online Solutions</t>
         </is>
       </c>
       <c r="E56" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Confirm%20Ticket%20Online%20Solutions%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AConfirm%20Ticket%20Online%20Solutions%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AConfirm%20Ticket%20Online%20Solutions%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Confirm%20Ticket%20Online%20Solutions</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2007,17 +2569,27 @@
           <t>Limeroad</t>
         </is>
       </c>
-      <c r="D57" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Limeroad%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Limeroad</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Limeroad%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALimeroad%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALimeroad%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Limeroad</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2033,17 +2605,27 @@
           <t>Nevilton Softech Private Limited</t>
         </is>
       </c>
-      <c r="D58" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nevilton%20Softech%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Nevilton Softech</t>
         </is>
       </c>
       <c r="E58" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nevilton%20Softech%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANevilton%20Softech%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANevilton%20Softech%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Nevilton%20Softech</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2059,17 +2641,27 @@
           <t>Godrej &amp; Boyce</t>
         </is>
       </c>
-      <c r="D59" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Godrej%20%26%20Boyce%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Godrej &amp; Boyce</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Godrej%20%26%20Boyce%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGodrej%20%26%20Boyce%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGodrej%20%26%20Boyce%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Godrej%20%26%20Boyce</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2085,17 +2677,27 @@
           <t>Alkem Laboratories Limited</t>
         </is>
       </c>
-      <c r="D60" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Alkem%20Laboratories%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Alkem Laboratories Limited</t>
         </is>
       </c>
       <c r="E60" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Alkem%20Laboratories%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAlkem%20Laboratories%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAlkem%20Laboratories%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Alkem%20Laboratories%20Limited</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2111,17 +2713,27 @@
           <t>FREIGHT TIGER</t>
         </is>
       </c>
-      <c r="D61" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22FREIGHT%20TIGER%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>FREIGHT TIGER</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22FREIGHT%20TIGER%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFREIGHT%20TIGER%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFREIGHT%20TIGER%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=FREIGHT%20TIGER</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2137,17 +2749,27 @@
           <t>Cashify</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cashify%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Cashify</t>
         </is>
       </c>
       <c r="E62" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cashify%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACashify%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACashify%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Cashify</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2163,17 +2785,27 @@
           <t>TCG Digital</t>
         </is>
       </c>
-      <c r="D63" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TCG%20Digital%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TCG Digital</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TCG%20Digital%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATCG%20Digital%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATCG%20Digital%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=TCG%20Digital</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2189,17 +2821,27 @@
           <t>Spicejet Limited</t>
         </is>
       </c>
-      <c r="D64" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spicejet%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Spicejet Limited</t>
         </is>
       </c>
       <c r="E64" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spicejet%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASpicejet%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASpicejet%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Spicejet%20Limited</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2215,17 +2857,27 @@
           <t>Nimbuspost</t>
         </is>
       </c>
-      <c r="D65" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nimbuspost%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Nimbuspost</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nimbuspost%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANimbuspost%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANimbuspost%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Nimbuspost</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2241,17 +2893,27 @@
           <t>More Retail</t>
         </is>
       </c>
-      <c r="D66" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22More%20Retail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>More Retail</t>
         </is>
       </c>
       <c r="E66" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22More%20Retail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMore%20Retail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMore%20Retail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=More%20Retail</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2267,17 +2929,27 @@
           <t>Cardekho.com(GirnarSoft Pvt. Limited )</t>
         </is>
       </c>
-      <c r="D67" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cardekho.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Cardekho.com</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cardekho.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACardekho.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACardekho.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Cardekho.com</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2293,17 +2965,27 @@
           <t>Abhibus Services (I) Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="D68" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Abhibus%20Services%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Abhibus Services</t>
         </is>
       </c>
       <c r="E68" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Abhibus%20Services%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAbhibus%20Services%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAbhibus%20Services%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Abhibus%20Services</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2319,17 +3001,27 @@
           <t>RENEW POWER PVT LTD</t>
         </is>
       </c>
-      <c r="D69" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22RENEW%20POWER%20PVT%20LTD%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RENEW POWER PVT LTD</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22RENEW%20POWER%20PVT%20LTD%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARENEW%20POWER%20PVT%20LTD%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARENEW%20POWER%20PVT%20LTD%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=RENEW%20POWER%20PVT%20LTD</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2345,17 +3037,27 @@
           <t>CureFit Healthcare Pvt Ltd</t>
         </is>
       </c>
-      <c r="D70" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CureFit%20Healthcare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CureFit Healthcare</t>
         </is>
       </c>
       <c r="E70" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CureFit%20Healthcare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACureFit%20Healthcare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACureFit%20Healthcare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=CureFit%20Healthcare</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2371,17 +3073,27 @@
           <t>Malabar Group</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Malabar%20Group%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Malabar Group</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Malabar%20Group%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMalabar%20Group%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMalabar%20Group%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Malabar%20Group</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2397,17 +3109,27 @@
           <t>Rebel Foods</t>
         </is>
       </c>
-      <c r="D72" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rebel%20Foods%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Rebel Foods</t>
         </is>
       </c>
       <c r="E72" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rebel%20Foods%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARebel%20Foods%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARebel%20Foods%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Rebel%20Foods</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2423,17 +3145,27 @@
           <t>Yamaha Motor India</t>
         </is>
       </c>
-      <c r="D73" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yamaha%20Motor%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Yamaha Motor India</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yamaha%20Motor%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AYamaha%20Motor%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AYamaha%20Motor%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Yamaha%20Motor%20India</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2449,17 +3181,27 @@
           <t>Daily Rounds</t>
         </is>
       </c>
-      <c r="D74" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Daily%20Rounds%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Daily Rounds</t>
         </is>
       </c>
       <c r="E74" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Daily%20Rounds%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADaily%20Rounds%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADaily%20Rounds%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Daily%20Rounds</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2475,17 +3217,27 @@
           <t>UPL LIMITED</t>
         </is>
       </c>
-      <c r="D75" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22UPL%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>UPL</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22UPL%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AUPL%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AUPL%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=UPL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2501,17 +3253,27 @@
           <t>nurture.farm</t>
         </is>
       </c>
-      <c r="D76" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22nurture.farm%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>nurture.farm</t>
         </is>
       </c>
       <c r="E76" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22nurture.farm%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3Anurture.farm%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3Anurture.farm%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=nurture.farm</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2527,17 +3289,27 @@
           <t>Hero Electronix Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="D77" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hero%20Electronix%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Hero Electronix</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hero%20Electronix%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHero%20Electronix%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHero%20Electronix%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G77" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Hero%20Electronix</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2553,17 +3325,27 @@
           <t>GRT Jewellers</t>
         </is>
       </c>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22GRT%20Jewellers%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>GRT Jewellers</t>
         </is>
       </c>
       <c r="E78" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22GRT%20Jewellers%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGRT%20Jewellers%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGRT%20Jewellers%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=GRT%20Jewellers</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2579,17 +3361,27 @@
           <t>EIH Ltd (Oberoi Hotels)</t>
         </is>
       </c>
-      <c r="D79" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22EIH%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EIH Ltd</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22EIH%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AEIH%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AEIH%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=EIH%20Ltd</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2605,17 +3397,27 @@
           <t>Green Agrevolution Private Limited</t>
         </is>
       </c>
-      <c r="D80" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Green%20Agrevolution%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Green Agrevolution</t>
         </is>
       </c>
       <c r="E80" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Green%20Agrevolution%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGreen%20Agrevolution%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGreen%20Agrevolution%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Green%20Agrevolution</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2631,17 +3433,27 @@
           <t>Pickrr</t>
         </is>
       </c>
-      <c r="D81" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pickrr%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pickrr</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pickrr%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APickrr%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APickrr%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Pickrr</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2657,17 +3469,27 @@
           <t>Healthians</t>
         </is>
       </c>
-      <c r="D82" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Healthians%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Healthians</t>
         </is>
       </c>
       <c r="E82" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Healthians%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHealthians%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHealthians%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Healthians</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2683,17 +3505,27 @@
           <t>SENCO</t>
         </is>
       </c>
-      <c r="D83" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SENCO%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SENCO%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASENCO%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASENCO%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=SENCO</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2709,17 +3541,27 @@
           <t>COCOBLU RETAIL LIMITED</t>
         </is>
       </c>
-      <c r="D84" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22COCOBLU%20RETAIL%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>COCOBLU RETAIL</t>
         </is>
       </c>
       <c r="E84" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22COCOBLU%20RETAIL%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACOCOBLU%20RETAIL%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACOCOBLU%20RETAIL%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=COCOBLU%20RETAIL</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2735,17 +3577,27 @@
           <t>Ashok Leyland</t>
         </is>
       </c>
-      <c r="D85" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Ashok%20Leyland%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Ashok Leyland</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Ashok%20Leyland%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAshok%20Leyland%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAshok%20Leyland%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Ashok%20Leyland</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2761,17 +3613,27 @@
           <t>BlueBrix Health</t>
         </is>
       </c>
-      <c r="D86" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlueBrix%20Health%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BlueBrix Health</t>
         </is>
       </c>
       <c r="E86" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlueBrix%20Health%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABlueBrix%20Health%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABlueBrix%20Health%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=BlueBrix%20Health</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2787,17 +3649,27 @@
           <t>Oyo Rooms</t>
         </is>
       </c>
-      <c r="D87" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Oyo%20Rooms%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Oyo Rooms</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Oyo%20Rooms%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AOyo%20Rooms%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AOyo%20Rooms%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Oyo%20Rooms</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2813,17 +3685,27 @@
           <t>Cashkaro.com</t>
         </is>
       </c>
-      <c r="D88" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cashkaro.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Cashkaro.com</t>
         </is>
       </c>
       <c r="E88" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cashkaro.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACashkaro.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACashkaro.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Cashkaro.com</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2839,17 +3721,27 @@
           <t>Kalyan Jewellers</t>
         </is>
       </c>
-      <c r="D89" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Kalyan%20Jewellers%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Kalyan Jewellers</t>
         </is>
       </c>
       <c r="E89" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Kalyan%20Jewellers%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AKalyan%20Jewellers%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AKalyan%20Jewellers%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G89" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Kalyan%20Jewellers</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2865,17 +3757,27 @@
           <t>Innova Market Insights</t>
         </is>
       </c>
-      <c r="D90" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Innova%20Market%20Insights%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Innova Market Insights</t>
         </is>
       </c>
       <c r="E90" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Innova%20Market%20Insights%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AInnova%20Market%20Insights%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AInnova%20Market%20Insights%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Innova%20Market%20Insights</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2891,17 +3793,27 @@
           <t>Imagine Marketing Pvt. Ltd (Boat)</t>
         </is>
       </c>
-      <c r="D91" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Imagine%20Marketing%20Pvt.%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Imagine Marketing Pvt. Ltd</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Imagine%20Marketing%20Pvt.%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AImagine%20Marketing%20Pvt.%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AImagine%20Marketing%20Pvt.%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G91" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Imagine%20Marketing%20Pvt.%20Ltd</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2917,17 +3829,27 @@
           <t>Lynk Logistics Pvt Ltd</t>
         </is>
       </c>
-      <c r="D92" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lynk%20Logistics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Lynk Logistics</t>
         </is>
       </c>
       <c r="E92" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lynk%20Logistics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALynk%20Logistics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALynk%20Logistics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G92" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Lynk%20Logistics</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2943,17 +3865,27 @@
           <t>Yatra.com</t>
         </is>
       </c>
-      <c r="D93" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yatra.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Yatra.com</t>
         </is>
       </c>
       <c r="E93" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yatra.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AYatra.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AYatra.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G93" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Yatra.com</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2969,17 +3901,27 @@
           <t>CLICKTECH RETAIL PRIVATE LIMITED</t>
         </is>
       </c>
-      <c r="D94" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CLICKTECH%20RETAIL%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CLICKTECH RETAIL</t>
         </is>
       </c>
       <c r="E94" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CLICKTECH%20RETAIL%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACLICKTECH%20RETAIL%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACLICKTECH%20RETAIL%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G94" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=CLICKTECH%20RETAIL</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2995,17 +3937,27 @@
           <t>TVS Supply Chain Solutions Limited</t>
         </is>
       </c>
-      <c r="D95" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TVS%20Supply%20Chain%20Solutions%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>TVS Supply Chain Solutions Limited</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TVS%20Supply%20Chain%20Solutions%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATVS%20Supply%20Chain%20Solutions%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATVS%20Supply%20Chain%20Solutions%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G95" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=TVS%20Supply%20Chain%20Solutions%20Limited</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3021,17 +3973,27 @@
           <t>Hatsun Agro Products</t>
         </is>
       </c>
-      <c r="D96" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hatsun%20Agro%20Products%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Hatsun Agro Products</t>
         </is>
       </c>
       <c r="E96" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hatsun%20Agro%20Products%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHatsun%20Agro%20Products%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHatsun%20Agro%20Products%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Hatsun%20Agro%20Products</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3047,17 +4009,27 @@
           <t>THERMAX LIMITED</t>
         </is>
       </c>
-      <c r="D97" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22THERMAX%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="E97" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22THERMAX%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATHERMAX%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATHERMAX%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G97" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=THERMAX</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3073,17 +4045,27 @@
           <t>Eatclub Brands</t>
         </is>
       </c>
-      <c r="D98" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Eatclub%20Brands%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Eatclub Brands</t>
         </is>
       </c>
       <c r="E98" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Eatclub%20Brands%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AEatclub%20Brands%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AEatclub%20Brands%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G98" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Eatclub%20Brands</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3099,17 +4081,27 @@
           <t>Jyothy Laboratories</t>
         </is>
       </c>
-      <c r="D99" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jyothy%20Laboratories%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Jyothy Laboratories</t>
         </is>
       </c>
       <c r="E99" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jyothy%20Laboratories%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AJyothy%20Laboratories%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F99" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AJyothy%20Laboratories%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G99" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Jyothy%20Laboratories</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3125,17 +4117,27 @@
           <t>Wellness Forever Medicare Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="D100" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wellness%20Forever%20Medicare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Wellness Forever Medicare</t>
         </is>
       </c>
       <c r="E100" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wellness%20Forever%20Medicare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AWellness%20Forever%20Medicare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AWellness%20Forever%20Medicare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G100" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Wellness%20Forever%20Medicare</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3151,17 +4153,27 @@
           <t>Bright Lifecare Pvt. Ltd.(HealthKart)</t>
         </is>
       </c>
-      <c r="D101" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bright%20Lifecare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Bright Lifecare</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bright%20Lifecare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABright%20Lifecare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F101" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABright%20Lifecare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G101" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Bright%20Lifecare</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3177,17 +4189,27 @@
           <t>Angara.com</t>
         </is>
       </c>
-      <c r="D102" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Angara.com%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Angara.com</t>
         </is>
       </c>
       <c r="E102" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Angara.com%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAngara.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAngara.com%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G102" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Angara.com</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3203,17 +4225,27 @@
           <t>Aliaxis - ASHIRVAD PIPES PVT. LTD.</t>
         </is>
       </c>
-      <c r="D103" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aliaxis%20-%20ASHIRVAD%20PIPES%20PVT.%20LTD.%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Aliaxis - ASHIRVAD PIPES PVT. LTD.</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aliaxis%20-%20ASHIRVAD%20PIPES%20PVT.%20LTD.%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAliaxis%20-%20ASHIRVAD%20PIPES%20PVT.%20LTD.%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F103" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAliaxis%20-%20ASHIRVAD%20PIPES%20PVT.%20LTD.%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G103" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Aliaxis%20-%20ASHIRVAD%20PIPES%20PVT.%20LTD.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3229,17 +4261,27 @@
           <t>Applied Research International Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="D104" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Applied%20Research%20International%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Applied Research International</t>
         </is>
       </c>
       <c r="E104" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Applied%20Research%20International%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AApplied%20Research%20International%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AApplied%20Research%20International%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Applied%20Research%20International</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3255,17 +4297,27 @@
           <t>Inventia Healthcare Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="D105" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Inventia%20Healthcare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Inventia Healthcare</t>
         </is>
       </c>
       <c r="E105" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Inventia%20Healthcare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AInventia%20Healthcare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F105" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AInventia%20Healthcare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Inventia%20Healthcare</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3281,17 +4333,27 @@
           <t>Hardcastle Restaurants Private Limited</t>
         </is>
       </c>
-      <c r="D106" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hardcastle%20Restaurants%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Hardcastle Restaurants</t>
         </is>
       </c>
       <c r="E106" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hardcastle%20Restaurants%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHardcastle%20Restaurants%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F106" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHardcastle%20Restaurants%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Hardcastle%20Restaurants</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3307,17 +4369,27 @@
           <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
-      <c r="D107" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Torrent%20Pharmaceuticals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals</t>
         </is>
       </c>
       <c r="E107" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Torrent%20Pharmaceuticals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATorrent%20Pharmaceuticals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F107" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATorrent%20Pharmaceuticals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G107" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Torrent%20Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3333,17 +4405,27 @@
           <t>Bajaj Electricals Ltd.</t>
         </is>
       </c>
-      <c r="D108" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bajaj%20Electricals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Bajaj Electricals</t>
         </is>
       </c>
       <c r="E108" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bajaj%20Electricals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABajaj%20Electricals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABajaj%20Electricals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G108" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Bajaj%20Electricals</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3359,17 +4441,27 @@
           <t>Rain Industries LIMITED</t>
         </is>
       </c>
-      <c r="D109" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rain%20Industries%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Rain Industries</t>
         </is>
       </c>
       <c r="E109" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rain%20Industries%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARain%20Industries%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F109" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARain%20Industries%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G109" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Rain%20Industries</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3385,17 +4477,27 @@
           <t>Dishman Pharmaceuticals and Chemicals Ltd.</t>
         </is>
       </c>
-      <c r="D110" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dishman%20Pharmaceuticals%20and%20Chemicals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Dishman Pharmaceuticals and Chemicals</t>
         </is>
       </c>
       <c r="E110" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dishman%20Pharmaceuticals%20and%20Chemicals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADishman%20Pharmaceuticals%20and%20Chemicals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADishman%20Pharmaceuticals%20and%20Chemicals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G110" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Dishman%20Pharmaceuticals%20and%20Chemicals</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3411,17 +4513,27 @@
           <t>Continue Lifesciences Private Limited</t>
         </is>
       </c>
-      <c r="D111" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Continue%20Lifesciences%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Continue Lifesciences</t>
         </is>
       </c>
       <c r="E111" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Continue%20Lifesciences%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AContinue%20Lifesciences%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F111" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AContinue%20Lifesciences%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G111" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Continue%20Lifesciences</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3437,17 +4549,27 @@
           <t>Brigade Enterprises Ltd</t>
         </is>
       </c>
-      <c r="D112" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Brigade%20Enterprises%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Brigade Enterprises Ltd</t>
         </is>
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Brigade%20Enterprises%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABrigade%20Enterprises%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABrigade%20Enterprises%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G112" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Brigade%20Enterprises%20Ltd</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3463,17 +4585,27 @@
           <t>Intermiles (Jet Privilege Private Limited)</t>
         </is>
       </c>
-      <c r="D113" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Intermiles%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Intermiles</t>
         </is>
       </c>
       <c r="E113" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Intermiles%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AIntermiles%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F113" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AIntermiles%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G113" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Intermiles</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3489,17 +4621,27 @@
           <t>Prestige Constructions</t>
         </is>
       </c>
-      <c r="D114" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Prestige%20Constructions%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Prestige Constructions</t>
         </is>
       </c>
       <c r="E114" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Prestige%20Constructions%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APrestige%20Constructions%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F114" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APrestige%20Constructions%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G114" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Prestige%20Constructions</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3515,17 +4657,27 @@
           <t>Gmmco Limited</t>
         </is>
       </c>
-      <c r="D115" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Gmmco%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Gmmco Limited</t>
         </is>
       </c>
       <c r="E115" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Gmmco%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGmmco%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F115" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGmmco%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G115" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Gmmco%20Limited</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3541,17 +4693,27 @@
           <t>Panasonic India</t>
         </is>
       </c>
-      <c r="D116" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Panasonic%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Panasonic India</t>
         </is>
       </c>
       <c r="E116" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Panasonic%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APanasonic%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APanasonic%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G116" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Panasonic%20India</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3567,17 +4729,27 @@
           <t>ReNew Power</t>
         </is>
       </c>
-      <c r="D117" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22ReNew%20Power%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ReNew Power</t>
         </is>
       </c>
       <c r="E117" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22ReNew%20Power%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AReNew%20Power%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AReNew%20Power%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G117" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=ReNew%20Power</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3593,17 +4765,27 @@
           <t>Aira Matrix</t>
         </is>
       </c>
-      <c r="D118" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aira%20Matrix%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Aira Matrix</t>
         </is>
       </c>
       <c r="E118" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aira%20Matrix%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAira%20Matrix%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAira%20Matrix%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G118" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Aira%20Matrix</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3619,17 +4801,27 @@
           <t>Torrent Power Ltd.</t>
         </is>
       </c>
-      <c r="D119" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Torrent%20Power%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Torrent Power</t>
         </is>
       </c>
       <c r="E119" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Torrent%20Power%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATorrent%20Power%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATorrent%20Power%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Torrent%20Power</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3645,17 +4837,27 @@
           <t>ECU Worldwide</t>
         </is>
       </c>
-      <c r="D120" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22ECU%20Worldwide%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ECU Worldwide</t>
         </is>
       </c>
       <c r="E120" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22ECU%20Worldwide%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AECU%20Worldwide%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AECU%20Worldwide%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G120" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=ECU%20Worldwide</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3671,17 +4873,27 @@
           <t>Honasa Consumer Pvt. Ltd</t>
         </is>
       </c>
-      <c r="D121" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Honasa%20Consumer%20Pvt.%20Ltd%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Honasa Consumer Pvt. Ltd</t>
         </is>
       </c>
       <c r="E121" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Honasa%20Consumer%20Pvt.%20Ltd%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHonasa%20Consumer%20Pvt.%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F121" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHonasa%20Consumer%20Pvt.%20Ltd%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G121" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Honasa%20Consumer%20Pvt.%20Ltd</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3697,17 +4909,27 @@
           <t>SYNGENE INTERNATIONAL LIMITED</t>
         </is>
       </c>
-      <c r="D122" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SYNGENE%20INTERNATIONAL%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SYNGENE INTERNATIONAL</t>
         </is>
       </c>
       <c r="E122" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SYNGENE%20INTERNATIONAL%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASYNGENE%20INTERNATIONAL%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASYNGENE%20INTERNATIONAL%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G122" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=SYNGENE%20INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3723,17 +4945,27 @@
           <t>Cadila Healthcare Ltd., Ahmedabad</t>
         </is>
       </c>
-      <c r="D123" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cadila%20Healthcare%20%2C%20Ahmedabad%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Cadila Healthcare Ahmedabad</t>
         </is>
       </c>
       <c r="E123" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cadila%20Healthcare%20%2C%20Ahmedabad%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACadila%20Healthcare%20Ahmedabad%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F123" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACadila%20Healthcare%20Ahmedabad%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G123" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Cadila%20Healthcare%20Ahmedabad</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3749,17 +4981,27 @@
           <t>Ceat Tyres Limited</t>
         </is>
       </c>
-      <c r="D124" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Ceat%20Tyres%20Limited%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Ceat Tyres Limited</t>
         </is>
       </c>
       <c r="E124" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Ceat%20Tyres%20Limited%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACeat%20Tyres%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACeat%20Tyres%20Limited%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G124" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Ceat%20Tyres%20Limited</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3775,17 +5017,27 @@
           <t>Honda Motorcycle and Scooter India</t>
         </is>
       </c>
-      <c r="D125" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Honda%20Motorcycle%20and%20Scooter%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Honda Motorcycle and Scooter India</t>
         </is>
       </c>
       <c r="E125" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Honda%20Motorcycle%20and%20Scooter%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHonda%20Motorcycle%20and%20Scooter%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F125" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHonda%20Motorcycle%20and%20Scooter%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G125" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Honda%20Motorcycle%20and%20Scooter%20India</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3801,17 +5053,27 @@
           <t>Heritage Foods Ltd.</t>
         </is>
       </c>
-      <c r="D126" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Heritage%20Foods%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Heritage Foods</t>
         </is>
       </c>
       <c r="E126" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Heritage%20Foods%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHeritage%20Foods%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHeritage%20Foods%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G126" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Heritage%20Foods</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3827,17 +5089,27 @@
           <t>CK Birla Hospitals</t>
         </is>
       </c>
-      <c r="D127" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CK%20Birla%20Hospitals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CK Birla Hospitals</t>
         </is>
       </c>
       <c r="E127" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CK%20Birla%20Hospitals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACK%20Birla%20Hospitals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F127" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACK%20Birla%20Hospitals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G127" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=CK%20Birla%20Hospitals</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3853,17 +5125,27 @@
           <t>Licious (Delightful Gourmet)</t>
         </is>
       </c>
-      <c r="D128" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Licious%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Licious</t>
         </is>
       </c>
       <c r="E128" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Licious%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALicious%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F128" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALicious%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G128" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Licious</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3879,17 +5161,27 @@
           <t>Country Delight</t>
         </is>
       </c>
-      <c r="D129" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Country%20Delight%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Country Delight</t>
         </is>
       </c>
       <c r="E129" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Country%20Delight%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACountry%20Delight%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F129" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACountry%20Delight%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G129" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Country%20Delight</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3905,17 +5197,27 @@
           <t>Truemeds</t>
         </is>
       </c>
-      <c r="D130" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Truemeds%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Truemeds</t>
         </is>
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Truemeds%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATruemeds%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATruemeds%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G130" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Truemeds</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3931,17 +5233,27 @@
           <t>Treebo Hotels</t>
         </is>
       </c>
-      <c r="D131" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Treebo%20Hotels%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Treebo Hotels</t>
         </is>
       </c>
       <c r="E131" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Treebo%20Hotels%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATreebo%20Hotels%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATreebo%20Hotels%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G131" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Treebo%20Hotels</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3957,17 +5269,27 @@
           <t>Yulu Bikes</t>
         </is>
       </c>
-      <c r="D132" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yulu%20Bikes%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Yulu Bikes</t>
         </is>
       </c>
       <c r="E132" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Yulu%20Bikes%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AYulu%20Bikes%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AYulu%20Bikes%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G132" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Yulu%20Bikes</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3983,17 +5305,27 @@
           <t>DealShare</t>
         </is>
       </c>
-      <c r="D133" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22DealShare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DealShare</t>
         </is>
       </c>
       <c r="E133" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22DealShare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADealShare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F133" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADealShare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G133" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=DealShare</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4009,17 +5341,27 @@
           <t>Spencer's Retail</t>
         </is>
       </c>
-      <c r="D134" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spencer%27s%20Retail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Spencer's Retail</t>
         </is>
       </c>
       <c r="E134" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spencer%27s%20Retail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASpencer%27s%20Retail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASpencer%27s%20Retail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G134" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Spencer%27s%20Retail</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4035,17 +5377,27 @@
           <t>Medanta (Global Health)</t>
         </is>
       </c>
-      <c r="D135" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Medanta%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Medanta</t>
         </is>
       </c>
       <c r="E135" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Medanta%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMedanta%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMedanta%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G135" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Medanta</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4061,17 +5413,27 @@
           <t>carandbike (Mahindra)</t>
         </is>
       </c>
-      <c r="D136" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22carandbike%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>carandbike</t>
         </is>
       </c>
       <c r="E136" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22carandbike%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3Acarandbike%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3Acarandbike%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=carandbike</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4087,17 +5449,27 @@
           <t>The Souled Store</t>
         </is>
       </c>
-      <c r="D137" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Souled%20Store%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>The Souled Store</t>
         </is>
       </c>
       <c r="E137" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Souled%20Store%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AThe%20Souled%20Store%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F137" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AThe%20Souled%20Store%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G137" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=The%20Souled%20Store</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4113,17 +5485,27 @@
           <t>Quick Ride</t>
         </is>
       </c>
-      <c r="D138" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Quick%20Ride%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Quick Ride</t>
         </is>
       </c>
       <c r="E138" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Quick%20Ride%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AQuick%20Ride%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AQuick%20Ride%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Quick%20Ride</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4139,17 +5521,27 @@
           <t>OfBusiness</t>
         </is>
       </c>
-      <c r="D139" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22OfBusiness%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>OfBusiness</t>
         </is>
       </c>
       <c r="E139" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22OfBusiness%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AOfBusiness%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F139" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AOfBusiness%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G139" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=OfBusiness</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4165,17 +5557,27 @@
           <t>Dr Lal PathLabs</t>
         </is>
       </c>
-      <c r="D140" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dr%20Lal%20PathLabs%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Dr Lal PathLabs</t>
         </is>
       </c>
       <c r="E140" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Dr%20Lal%20PathLabs%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADr%20Lal%20PathLabs%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ADr%20Lal%20PathLabs%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G140" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Dr%20Lal%20PathLabs</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4191,17 +5593,27 @@
           <t>Orange Health Labs</t>
         </is>
       </c>
-      <c r="D141" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Orange%20Health%20Labs%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Orange Health Labs</t>
         </is>
       </c>
       <c r="E141" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Orange%20Health%20Labs%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AOrange%20Health%20Labs%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AOrange%20Health%20Labs%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G141" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Orange%20Health%20Labs</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4217,17 +5629,27 @@
           <t>Medikabazaar</t>
         </is>
       </c>
-      <c r="D142" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Medikabazaar%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Medikabazaar</t>
         </is>
       </c>
       <c r="E142" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Medikabazaar%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMedikabazaar%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMedikabazaar%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G142" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Medikabazaar</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4243,17 +5665,27 @@
           <t>Woodland (Aero Club)</t>
         </is>
       </c>
-      <c r="D143" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Woodland%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Woodland</t>
         </is>
       </c>
       <c r="E143" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Woodland%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AWoodland%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AWoodland%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G143" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Woodland</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4269,17 +5701,27 @@
           <t>FarMart</t>
         </is>
       </c>
-      <c r="D144" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22FarMart%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>FarMart</t>
         </is>
       </c>
       <c r="E144" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22FarMart%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFarMart%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFarMart%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=FarMart</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4295,17 +5737,27 @@
           <t>Nature's Basket</t>
         </is>
       </c>
-      <c r="D145" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nature%27s%20Basket%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Nature's Basket</t>
         </is>
       </c>
       <c r="E145" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nature%27s%20Basket%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANature%27s%20Basket%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F145" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANature%27s%20Basket%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G145" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Nature%27s%20Basket</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4321,17 +5773,27 @@
           <t>Hopscotch</t>
         </is>
       </c>
-      <c r="D146" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hopscotch%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Hopscotch</t>
         </is>
       </c>
       <c r="E146" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Hopscotch%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHopscotch%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F146" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHopscotch%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G146" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Hopscotch</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4347,17 +5809,27 @@
           <t>Orient Electric</t>
         </is>
       </c>
-      <c r="D147" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Orient%20Electric%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Orient Electric</t>
         </is>
       </c>
       <c r="E147" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Orient%20Electric%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AOrient%20Electric%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AOrient%20Electric%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Orient%20Electric</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4373,17 +5845,27 @@
           <t>BOX8 (Eatsure)</t>
         </is>
       </c>
-      <c r="D148" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22BOX8%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>BOX8</t>
         </is>
       </c>
       <c r="E148" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22BOX8%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABOX8%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F148" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABOX8%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G148" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=BOX8</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4399,17 +5881,27 @@
           <t>Shipsy</t>
         </is>
       </c>
-      <c r="D149" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shipsy%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="E149" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shipsy%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AShipsy%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F149" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AShipsy%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G149" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Shipsy</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4425,17 +5917,27 @@
           <t>Locus</t>
         </is>
       </c>
-      <c r="D150" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Locus%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Locus</t>
         </is>
       </c>
       <c r="E150" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Locus%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALocus%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALocus%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G150" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Locus</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4451,17 +5953,27 @@
           <t>Moglix</t>
         </is>
       </c>
-      <c r="D151" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Moglix%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Moglix</t>
         </is>
       </c>
       <c r="E151" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Moglix%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMoglix%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMoglix%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G151" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Moglix</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4477,17 +5989,27 @@
           <t>Metropolis Healthcare</t>
         </is>
       </c>
-      <c r="D152" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Metropolis%20Healthcare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Metropolis Healthcare</t>
         </is>
       </c>
       <c r="E152" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Metropolis%20Healthcare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMetropolis%20Healthcare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F152" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMetropolis%20Healthcare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G152" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Metropolis%20Healthcare</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4503,17 +6025,27 @@
           <t>AgroStar</t>
         </is>
       </c>
-      <c r="D153" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22AgroStar%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>AgroStar</t>
         </is>
       </c>
       <c r="E153" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22AgroStar%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAgroStar%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAgroStar%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G153" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=AgroStar</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4529,17 +6061,27 @@
           <t>Akshayakalpa Organic</t>
         </is>
       </c>
-      <c r="D154" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akshayakalpa%20Organic%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
         </is>
       </c>
       <c r="E154" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akshayakalpa%20Organic%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAkshayakalpa%20Organic%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F154" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAkshayakalpa%20Organic%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Akshayakalpa%20Organic</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4555,17 +6097,27 @@
           <t>CaratLane</t>
         </is>
       </c>
-      <c r="D155" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CaratLane%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CaratLane</t>
         </is>
       </c>
       <c r="E155" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CaratLane%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACaratLane%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F155" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACaratLane%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G155" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=CaratLane</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4581,17 +6133,27 @@
           <t>Foxtale</t>
         </is>
       </c>
-      <c r="D156" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Foxtale%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Foxtale</t>
         </is>
       </c>
       <c r="E156" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Foxtale%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFoxtale%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F156" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFoxtale%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Foxtale</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4607,17 +6169,27 @@
           <t>CityMall</t>
         </is>
       </c>
-      <c r="D157" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CityMall%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CityMall</t>
         </is>
       </c>
       <c r="E157" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CityMall%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACityMall%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACityMall%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G157" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=CityMall</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4633,17 +6205,27 @@
           <t>Vegrow</t>
         </is>
       </c>
-      <c r="D158" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vegrow%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Vegrow</t>
         </is>
       </c>
       <c r="E158" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vegrow%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVegrow%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F158" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVegrow%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G158" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Vegrow</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4659,17 +6241,27 @@
           <t>Shree Maruti Courier</t>
         </is>
       </c>
-      <c r="D159" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shree%20Maruti%20Courier%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Shree Maruti Courier</t>
         </is>
       </c>
       <c r="E159" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shree%20Maruti%20Courier%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AShree%20Maruti%20Courier%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F159" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AShree%20Maruti%20Courier%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G159" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Shree%20Maruti%20Courier</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4685,17 +6277,27 @@
           <t>Pickyourtrail</t>
         </is>
       </c>
-      <c r="D160" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pickyourtrail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Pickyourtrail</t>
         </is>
       </c>
       <c r="E160" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pickyourtrail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APickyourtrail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F160" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APickyourtrail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Pickyourtrail</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4711,17 +6313,27 @@
           <t>Urban Ladder</t>
         </is>
       </c>
-      <c r="D161" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Urban%20Ladder%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Urban Ladder</t>
         </is>
       </c>
       <c r="E161" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Urban%20Ladder%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AUrban%20Ladder%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F161" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AUrban%20Ladder%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G161" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Urban%20Ladder</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4737,17 +6349,27 @@
           <t>BlueStone</t>
         </is>
       </c>
-      <c r="D162" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlueStone%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>BlueStone</t>
         </is>
       </c>
       <c r="E162" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlueStone%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABlueStone%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F162" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABlueStone%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G162" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=BlueStone</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4763,17 +6385,27 @@
           <t>Zivame</t>
         </is>
       </c>
-      <c r="D163" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zivame%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Zivame</t>
         </is>
       </c>
       <c r="E163" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zivame%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZivame%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F163" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZivame%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G163" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Zivame</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4789,17 +6421,27 @@
           <t>Clovia</t>
         </is>
       </c>
-      <c r="D164" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Clovia%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Clovia</t>
         </is>
       </c>
       <c r="E164" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Clovia%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AClovia%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F164" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AClovia%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G164" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Clovia</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4815,17 +6457,27 @@
           <t>Noise</t>
         </is>
       </c>
-      <c r="D165" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Noise%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Noise</t>
         </is>
       </c>
       <c r="E165" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Noise%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANoise%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F165" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANoise%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G165" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Noise</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4841,17 +6493,27 @@
           <t>Chai Point</t>
         </is>
       </c>
-      <c r="D166" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Chai%20Point%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
         </is>
       </c>
       <c r="E166" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Chai%20Point%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AChai%20Point%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F166" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AChai%20Point%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G166" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Chai%20Point</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4867,17 +6529,27 @@
           <t>BlackBuck (Zinka Logistics)</t>
         </is>
       </c>
-      <c r="D167" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlackBuck%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BlackBuck</t>
         </is>
       </c>
       <c r="E167" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22BlackBuck%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABlackBuck%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F167" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABlackBuck%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G167" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=BlackBuck</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4893,17 +6565,27 @@
           <t>Veena World</t>
         </is>
       </c>
-      <c r="D168" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Veena%20World%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Veena World</t>
         </is>
       </c>
       <c r="E168" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Veena%20World%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVeena%20World%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F168" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVeena%20World%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G168" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Veena%20World</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4919,17 +6601,27 @@
           <t>Zostel</t>
         </is>
       </c>
-      <c r="D169" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zostel%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Zostel</t>
         </is>
       </c>
       <c r="E169" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zostel%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZostel%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F169" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZostel%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G169" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Zostel</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4945,17 +6637,27 @@
           <t>Revv</t>
         </is>
       </c>
-      <c r="D170" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Revv%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Revv</t>
         </is>
       </c>
       <c r="E170" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Revv%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARevv%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F170" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARevv%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G170" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Revv</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4971,17 +6673,27 @@
           <t>Cogoport</t>
         </is>
       </c>
-      <c r="D171" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cogoport%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Cogoport</t>
         </is>
       </c>
       <c r="E171" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Cogoport%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACogoport%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F171" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACogoport%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G171" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Cogoport</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4997,17 +6709,27 @@
           <t>Zetwerk</t>
         </is>
       </c>
-      <c r="D172" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zetwerk%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Zetwerk</t>
         </is>
       </c>
       <c r="E172" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zetwerk%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZetwerk%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F172" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZetwerk%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G172" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Zetwerk</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5023,17 +6745,27 @@
           <t>Bizongo</t>
         </is>
       </c>
-      <c r="D173" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bizongo%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Bizongo</t>
         </is>
       </c>
       <c r="E173" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Bizongo%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABizongo%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABizongo%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G173" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Bizongo</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5049,17 +6781,27 @@
           <t>Pristyn Care</t>
         </is>
       </c>
-      <c r="D174" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pristyn%20Care%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Pristyn Care</t>
         </is>
       </c>
       <c r="E174" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pristyn%20Care%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APristyn%20Care%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F174" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APristyn%20Care%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G174" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Pristyn%20Care</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5075,17 +6817,27 @@
           <t>Vijay Sales</t>
         </is>
       </c>
-      <c r="D175" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vijay%20Sales%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Vijay Sales</t>
         </is>
       </c>
       <c r="E175" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Vijay%20Sales%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVijay%20Sales%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F175" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVijay%20Sales%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G175" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Vijay%20Sales</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5101,17 +6853,27 @@
           <t>Voylla</t>
         </is>
       </c>
-      <c r="D176" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Voylla%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Voylla</t>
         </is>
       </c>
       <c r="E176" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Voylla%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVoylla%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F176" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVoylla%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G176" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Voylla</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5127,17 +6889,27 @@
           <t>Blue Tokai Coffee</t>
         </is>
       </c>
-      <c r="D177" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Blue%20Tokai%20Coffee%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Blue Tokai Coffee</t>
         </is>
       </c>
       <c r="E177" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Blue%20Tokai%20Coffee%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABlue%20Tokai%20Coffee%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F177" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABlue%20Tokai%20Coffee%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G177" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Blue%20Tokai%20Coffee</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5153,17 +6925,27 @@
           <t>HealthifyMe</t>
         </is>
       </c>
-      <c r="D178" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22HealthifyMe%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>HealthifyMe</t>
         </is>
       </c>
       <c r="E178" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22HealthifyMe%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHealthifyMe%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F178" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AHealthifyMe%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G178" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=HealthifyMe</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5179,17 +6961,27 @@
           <t>Fitterfly</t>
         </is>
       </c>
-      <c r="D179" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Fitterfly%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Fitterfly</t>
         </is>
       </c>
       <c r="E179" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Fitterfly%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFitterfly%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F179" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFitterfly%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G179" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Fitterfly</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5205,17 +6997,27 @@
           <t>MFine</t>
         </is>
       </c>
-      <c r="D180" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22MFine%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>MFine</t>
         </is>
       </c>
       <c r="E180" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22MFine%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMFine%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F180" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMFine%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G180" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=MFine</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5231,17 +7033,27 @@
           <t>Zeno Health</t>
         </is>
       </c>
-      <c r="D181" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zeno%20Health%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Zeno Health</t>
         </is>
       </c>
       <c r="E181" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zeno%20Health%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZeno%20Health%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F181" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZeno%20Health%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G181" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Zeno%20Health</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5257,17 +7069,27 @@
           <t>Khadim's</t>
         </is>
       </c>
-      <c r="D182" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Khadim%27s%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Khadim's</t>
         </is>
       </c>
       <c r="E182" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Khadim%27s%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AKhadim%27s%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F182" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AKhadim%27s%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G182" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Khadim%27s</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5283,17 +7105,27 @@
           <t>Aditya Birla Fashion (Pantaloons, Allen Solly, Peter England, Van Heusen, Louis Philippe – all on Route 53/ap-south-1)</t>
         </is>
       </c>
-      <c r="D183" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aditya%20Birla%20Fashion%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Aditya Birla Fashion</t>
         </is>
       </c>
       <c r="E183" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aditya%20Birla%20Fashion%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAditya%20Birla%20Fashion%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F183" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAditya%20Birla%20Fashion%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G183" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Aditya%20Birla%20Fashion</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5309,17 +7141,27 @@
           <t>La Pino'z Pizza</t>
         </is>
       </c>
-      <c r="D184" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22La%20Pino%27z%20Pizza%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>La Pino'z Pizza</t>
         </is>
       </c>
       <c r="E184" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22La%20Pino%27z%20Pizza%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALa%20Pino%27z%20Pizza%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F184" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALa%20Pino%27z%20Pizza%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G184" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=La%20Pino%27z%20Pizza</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5335,17 +7177,27 @@
           <t>Lybrate</t>
         </is>
       </c>
-      <c r="D185" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lybrate%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Lybrate</t>
         </is>
       </c>
       <c r="E185" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Lybrate%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALybrate%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F185" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ALybrate%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G185" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Lybrate</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5361,17 +7213,27 @@
           <t>Rainbow Children's Hospital</t>
         </is>
       </c>
-      <c r="D186" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rainbow%20Children%27s%20Hospital%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Rainbow Children's Hospital</t>
         </is>
       </c>
       <c r="E186" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Rainbow%20Children%27s%20Hospital%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARainbow%20Children%27s%20Hospital%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F186" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARainbow%20Children%27s%20Hospital%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G186" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Rainbow%20Children%27s%20Hospital</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5387,17 +7249,27 @@
           <t>Aster DM Healthcare</t>
         </is>
       </c>
-      <c r="D187" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aster%20DM%20Healthcare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Aster DM Healthcare</t>
         </is>
       </c>
       <c r="E187" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Aster%20DM%20Healthcare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAster%20DM%20Healthcare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F187" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAster%20DM%20Healthcare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G187" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Aster%20DM%20Healthcare</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5413,17 +7285,27 @@
           <t>VLCC Personal Care</t>
         </is>
       </c>
-      <c r="D188" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22VLCC%20Personal%20Care%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>VLCC Personal Care</t>
         </is>
       </c>
       <c r="E188" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22VLCC%20Personal%20Care%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVLCC%20Personal%20Care%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F188" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AVLCC%20Personal%20Care%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G188" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=VLCC%20Personal%20Care</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5439,17 +7321,27 @@
           <t>Titan Eye+</t>
         </is>
       </c>
-      <c r="D189" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Titan%20Eye%2B%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Titan Eye</t>
         </is>
       </c>
       <c r="E189" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Titan%20Eye%2B%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATitan%20Eye%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F189" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATitan%20Eye%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G189" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Titan%20Eye</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5465,17 +7357,27 @@
           <t>Godrej Interio</t>
         </is>
       </c>
-      <c r="D190" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Godrej%20Interio%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Godrej Interio</t>
         </is>
       </c>
       <c r="E190" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Godrej%20Interio%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGodrej%20Interio%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F190" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGodrej%20Interio%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G190" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Godrej%20Interio</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5491,17 +7393,27 @@
           <t>Berger Paints</t>
         </is>
       </c>
-      <c r="D191" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Berger%20Paints%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Berger Paints</t>
         </is>
       </c>
       <c r="E191" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Berger%20Paints%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABerger%20Paints%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F191" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ABerger%20Paints%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G191" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Berger%20Paints</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5517,17 +7429,27 @@
           <t>Greenply Industries</t>
         </is>
       </c>
-      <c r="D192" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Greenply%20Industries%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Greenply Industries</t>
         </is>
       </c>
       <c r="E192" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Greenply%20Industries%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGreenply%20Industries%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F192" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AGreenply%20Industries%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G192" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Greenply%20Industries</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5543,17 +7465,27 @@
           <t>Trackon Couriers</t>
         </is>
       </c>
-      <c r="D193" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Trackon%20Couriers%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Trackon Couriers</t>
         </is>
       </c>
       <c r="E193" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Trackon%20Couriers%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATrackon%20Couriers%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F193" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATrackon%20Couriers%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G193" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Trackon%20Couriers</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5569,17 +7501,27 @@
           <t>Pepperfry</t>
         </is>
       </c>
-      <c r="D194" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pepperfry%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Pepperfry</t>
         </is>
       </c>
       <c r="E194" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Pepperfry%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APepperfry%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F194" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APepperfry%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G194" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Pepperfry</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5595,17 +7537,27 @@
           <t>Wakefit</t>
         </is>
       </c>
-      <c r="D195" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wakefit%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Wakefit</t>
         </is>
       </c>
       <c r="E195" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wakefit%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AWakefit%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F195" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AWakefit%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G195" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Wakefit</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5621,17 +7573,27 @@
           <t>Wow! Momo</t>
         </is>
       </c>
-      <c r="D196" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wow%21%20Momo%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Wow Momo</t>
         </is>
       </c>
       <c r="E196" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Wow%21%20Momo%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AWow%20Momo%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F196" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AWow%20Momo%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G196" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Wow%20Momo</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5647,17 +7609,27 @@
           <t>XpressBees</t>
         </is>
       </c>
-      <c r="D197" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22XpressBees%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>XpressBees</t>
         </is>
       </c>
       <c r="E197" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22XpressBees%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AXpressBees%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F197" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AXpressBees%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G197" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=XpressBees</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5673,17 +7645,27 @@
           <t>Shadowfax</t>
         </is>
       </c>
-      <c r="D198" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shadowfax%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Shadowfax</t>
         </is>
       </c>
       <c r="E198" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Shadowfax%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AShadowfax%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F198" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AShadowfax%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G198" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Shadowfax</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5699,17 +7681,27 @@
           <t>iThink Logistics</t>
         </is>
       </c>
-      <c r="D199" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22iThink%20Logistics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>iThink Logistics</t>
         </is>
       </c>
       <c r="E199" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22iThink%20Logistics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AiThink%20Logistics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F199" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AiThink%20Logistics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G199" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=iThink%20Logistics</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5725,17 +7717,27 @@
           <t>Akbar Travels</t>
         </is>
       </c>
-      <c r="D200" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akbar%20Travels%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Akbar Travels</t>
         </is>
       </c>
       <c r="E200" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Akbar%20Travels%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAkbar%20Travels%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F200" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AAkbar%20Travels%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G200" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Akbar%20Travels</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5751,17 +7753,27 @@
           <t>FarEye</t>
         </is>
       </c>
-      <c r="D201" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22FarEye%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>FarEye</t>
         </is>
       </c>
       <c r="E201" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22FarEye%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFarEye%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F201" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AFarEye%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G201" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=FarEye</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5777,17 +7789,27 @@
           <t>Jumbotail</t>
         </is>
       </c>
-      <c r="D202" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jumbotail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Jumbotail</t>
         </is>
       </c>
       <c r="E202" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Jumbotail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AJumbotail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F202" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AJumbotail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G202" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Jumbotail</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5803,17 +7825,27 @@
           <t>Thyrocare</t>
         </is>
       </c>
-      <c r="D203" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Thyrocare%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Thyrocare</t>
         </is>
       </c>
       <c r="E203" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Thyrocare%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AThyrocare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F203" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AThyrocare%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G203" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Thyrocare</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5829,17 +7861,27 @@
           <t>Manipal Hospitals</t>
         </is>
       </c>
-      <c r="D204" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Manipal%20Hospitals%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Manipal Hospitals</t>
         </is>
       </c>
       <c r="E204" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Manipal%20Hospitals%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AManipal%20Hospitals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F204" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AManipal%20Hospitals%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G204" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Manipal%20Hospitals</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5855,17 +7897,27 @@
           <t>CarInfo</t>
         </is>
       </c>
-      <c r="D205" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CarInfo%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CarInfo</t>
         </is>
       </c>
       <c r="E205" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22CarInfo%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACarInfo%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F205" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ACarInfo%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G205" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=CarInfo</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5881,17 +7933,27 @@
           <t>Park+</t>
         </is>
       </c>
-      <c r="D206" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Park%2B%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Park</t>
         </is>
       </c>
       <c r="E206" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Park%2B%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APark%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F206" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APark%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G206" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Park</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5907,17 +7969,27 @@
           <t>Sangeetha Mobiles</t>
         </is>
       </c>
-      <c r="D207" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sangeetha%20Mobiles%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Sangeetha Mobiles</t>
         </is>
       </c>
       <c r="E207" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sangeetha%20Mobiles%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASangeetha%20Mobiles%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F207" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASangeetha%20Mobiles%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G207" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Sangeetha%20Mobiles</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5933,17 +8005,27 @@
           <t>The Whole Truth Foods</t>
         </is>
       </c>
-      <c r="D208" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Whole%20Truth%20Foods%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>The Whole Truth Foods</t>
         </is>
       </c>
       <c r="E208" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Whole%20Truth%20Foods%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AThe%20Whole%20Truth%20Foods%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F208" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AThe%20Whole%20Truth%20Foods%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G208" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=The%20Whole%20Truth%20Foods</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5959,17 +8041,27 @@
           <t>Raw Pressery</t>
         </is>
       </c>
-      <c r="D209" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Raw%20Pressery%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Raw Pressery</t>
         </is>
       </c>
       <c r="E209" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Raw%20Pressery%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARaw%20Pressery%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F209" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARaw%20Pressery%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G209" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Raw%20Pressery</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5985,17 +8077,27 @@
           <t>Nestasia</t>
         </is>
       </c>
-      <c r="D210" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nestasia%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Nestasia</t>
         </is>
       </c>
       <c r="E210" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Nestasia%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANestasia%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F210" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANestasia%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G210" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Nestasia</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6011,17 +8113,27 @@
           <t>KisanKonnect</t>
         </is>
       </c>
-      <c r="D211" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22KisanKonnect%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>KisanKonnect</t>
         </is>
       </c>
       <c r="E211" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22KisanKonnect%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AKisanKonnect%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F211" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AKisanKonnect%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G211" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=KisanKonnect</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6037,17 +8149,27 @@
           <t>Raymond</t>
         </is>
       </c>
-      <c r="D212" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Raymond%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Raymond</t>
         </is>
       </c>
       <c r="E212" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Raymond%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARaymond%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F212" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ARaymond%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G212" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Raymond</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6063,17 +8185,27 @@
           <t>V-Guard Industries</t>
         </is>
       </c>
-      <c r="D213" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22V-Guard%20Industries%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>V-Guard Industries</t>
         </is>
       </c>
       <c r="E213" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22V-Guard%20Industries%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AV-Guard%20Industries%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F213" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AV-Guard%20Industries%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G213" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=V-Guard%20Industries</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6089,17 +8221,27 @@
           <t>Spoton Logistics</t>
         </is>
       </c>
-      <c r="D214" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spoton%20Logistics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Spoton Logistics</t>
         </is>
       </c>
       <c r="E214" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Spoton%20Logistics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASpoton%20Logistics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F214" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASpoton%20Logistics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G214" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Spoton%20Logistics</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6115,17 +8257,27 @@
           <t>TripFactory</t>
         </is>
       </c>
-      <c r="D215" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TripFactory%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>TripFactory</t>
         </is>
       </c>
       <c r="E215" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22TripFactory%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATripFactory%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F215" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ATripFactory%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G215" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=TripFactory</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6141,17 +8293,27 @@
           <t>Plum Goodness</t>
         </is>
       </c>
-      <c r="D216" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Plum%20Goodness%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Plum Goodness</t>
         </is>
       </c>
       <c r="E216" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Plum%20Goodness%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APlum%20Goodness%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F216" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3APlum%20Goodness%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G216" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Plum%20Goodness</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6167,17 +8329,27 @@
           <t>Zoomcar</t>
         </is>
       </c>
-      <c r="D217" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zoomcar%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Zoomcar</t>
         </is>
       </c>
       <c r="E217" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Zoomcar%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZoomcar%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F217" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AZoomcar%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G217" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Zoomcar</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6193,17 +8365,27 @@
           <t>V-Mart Retail</t>
         </is>
       </c>
-      <c r="D218" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22V-Mart%20Retail%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>V-Mart Retail</t>
         </is>
       </c>
       <c r="E218" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22V-Mart%20Retail%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AV-Mart%20Retail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F218" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AV-Mart%20Retail%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G218" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=V-Mart%20Retail</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6219,17 +8401,27 @@
           <t>SuperK</t>
         </is>
       </c>
-      <c r="D219" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SuperK%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SuperK</t>
         </is>
       </c>
       <c r="E219" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SuperK%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASuperK%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F219" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASuperK%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G219" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=SuperK</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6245,17 +8437,27 @@
           <t>Naturals Salon</t>
         </is>
       </c>
-      <c r="D220" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Naturals%20Salon%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Naturals Salon</t>
         </is>
       </c>
       <c r="E220" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Naturals%20Salon%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANaturals%20Salon%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F220" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ANaturals%20Salon%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G220" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Naturals%20Salon</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6271,17 +8473,27 @@
           <t>The Body Shop India</t>
         </is>
       </c>
-      <c r="D221" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Body%20Shop%20India%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>The Body Shop India</t>
         </is>
       </c>
       <c r="E221" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22The%20Body%20Shop%20India%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AThe%20Body%20Shop%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F221" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AThe%20Body%20Shop%20India%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G221" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=The%20Body%20Shop%20India</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6297,17 +8509,27 @@
           <t>Forest Essentials</t>
         </is>
       </c>
-      <c r="D222" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Forest%20Essentials%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Forest Essentials</t>
         </is>
       </c>
       <c r="E222" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Forest%20Essentials%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AForest%20Essentials%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F222" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AForest%20Essentials%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G222" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Forest%20Essentials</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6323,17 +8545,27 @@
           <t>Safexpress</t>
         </is>
       </c>
-      <c r="D223" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Safexpress%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Safexpress</t>
         </is>
       </c>
       <c r="E223" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Safexpress%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASafexpress%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F223" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASafexpress%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G223" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Safexpress</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6349,17 +8581,27 @@
           <t>Sarovar Hotels</t>
         </is>
       </c>
-      <c r="D224" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sarovar%20Hotels%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Sarovar Hotels</t>
         </is>
       </c>
       <c r="E224" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Sarovar%20Hotels%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASarovar%20Hotels%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F224" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASarovar%20Hotels%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G224" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Sarovar%20Hotels</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6375,17 +8617,27 @@
           <t>SUGAR Cosmetics</t>
         </is>
       </c>
-      <c r="D225" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SUGAR%20Cosmetics%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SUGAR Cosmetics</t>
         </is>
       </c>
       <c r="E225" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22SUGAR%20Cosmetics%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASUGAR%20Cosmetics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F225" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3ASUGAR%20Cosmetics%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G225" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=SUGAR%20Cosmetics</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6401,17 +8653,27 @@
           <t>Emami</t>
         </is>
       </c>
-      <c r="D226" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Emami%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Emami</t>
         </is>
       </c>
       <c r="E226" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Emami%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AEmami%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F226" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AEmami%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G226" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Emami</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6427,472 +8689,708 @@
           <t>Melorra</t>
         </is>
       </c>
-      <c r="D227" s="18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Melorra%22%20%28CTO%20OR%20CIO%20OR%20%22Chief%20Technology%22%20OR%20%22Chief%20Information%22%20OR%20%22Chief%20Digital%22%20OR%20%22VP%20Engineering%22%20OR%20%22Head%20of%20Engineering%22%20OR%20%22Head%20of%20IT%22%20OR%20%22Head%20of%20Infrastructure%22%20OR%20%22Cloud%22%20OR%20%22DevOps%22%29</t>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Melorra</t>
         </is>
       </c>
       <c r="E227" s="18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/sales/search/people?keywords=%22Melorra%22%20%28CEO%20OR%20Founder%20OR%20%22Co-founder%22%20OR%20CFO%20OR%20%22Managing%20Director%22%29</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr"/>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMelorra%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3AFUNCTION%2Cvalues%3AList%28%28id%3A13%2CselectionType%3AINCLUDED%29%2C%28id%3A8%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="F227" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?query=%28filters%3AList%28%28type%3ACURRENT_COMPANY%2Cvalues%3AList%28%28text%3AMelorra%2CselectionType%3AINCLUDED%29%29%29%2C%28type%3ASENIORITY_LEVEL%2Cvalues%3AList%28%28id%3A310%2CselectionType%3AINCLUDED%29%2C%28id%3A300%2CselectionType%3AINCLUDED%29%2C%28id%3A220%2CselectionType%3AINCLUDED%29%2C%28id%3A320%2CselectionType%3AINCLUDED%29%29%29%29%29</t>
+        </is>
+      </c>
+      <c r="G227" s="18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/sales/search/people?keywords=Melorra</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F125" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F126" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F127" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F128" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F129" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F130" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F131" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F132" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F133" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F134" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F135" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F136" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F137" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F138" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F139" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F140" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F141" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F142" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F143" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F144" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F145" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F146" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F147" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F148" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F149" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F150" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F151" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F152" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F153" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F154" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F155" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F156" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F157" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F158" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F159" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F160" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F161" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F162" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F163" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F164" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F165" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F166" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F167" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F168" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F169" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F170" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F171" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F172" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F173" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F174" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F175" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F176" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F177" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F178" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F179" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F180" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F181" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F182" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F183" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F184" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F185" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F186" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F187" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F188" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F189" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F190" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F191" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F192" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F193" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F194" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F195" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId678"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
